--- a/database_manutenzione.xlsx
+++ b/database_manutenzione.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivanc\OneDrive\Desktop\pdf_manutenzione\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ivanc\OneDrive\Desktop\manutenzione_web\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,9 +36,6 @@
     <t>ODS</t>
   </si>
   <si>
-    <t>F1_rev.16</t>
-  </si>
-  <si>
     <t>Struttura cassa</t>
   </si>
   <si>
@@ -241,9 +238,6 @@
   </si>
   <si>
     <t>ian 5 Copiglia ,</t>
-  </si>
-  <si>
-    <t>F2_rev16</t>
   </si>
   <si>
     <t>Struttura cassa Verifica integrita carenature e finestrini s Mv-270 | MV005</t>
@@ -1338,6 +1332,12 @@
   </si>
   <si>
     <t>ETR1000-V300ZEF. ANNESSO- MR1-01A-TC001</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>F2</t>
   </si>
 </sst>
 </file>
@@ -1819,3098 +1819,3098 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>385</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>312</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="C45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="C46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="C47" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" t="s">
         <v>70</v>
-      </c>
-      <c r="D47" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>416</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C50" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>417</v>
+      </c>
+      <c r="C51" t="s">
         <v>74</v>
       </c>
-      <c r="C51" t="s">
-        <v>76</v>
-      </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C54" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D54" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D55" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C57" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C58" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D58" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D60" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C61" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D62" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D65" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C66" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D66" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C67" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D68" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C69" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D69" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C70" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D70" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C71" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C72" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C73" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D73" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C74" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D74" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C75" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C77" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D77" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C78" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D78" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C79" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C80" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D80" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D82" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C83" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D83" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D84" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C85" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C86" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D86" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C87" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D87" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C88" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D88" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C89" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C90" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D90" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C91" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D91" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C92" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C93" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D93" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C94" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D94" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C95" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D95" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C96" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C97" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C98" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D98" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C99" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D99" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C100" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D100" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C101" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D101" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C102" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C103" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D103" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C104" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C105" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D105" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C106" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C107" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C108" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D108" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C109" t="s">
+        <v>56</v>
+      </c>
+      <c r="D109" t="s">
         <v>57</v>
-      </c>
-      <c r="D109" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C110" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D110" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C111" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D111" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C112" t="s">
+        <v>60</v>
+      </c>
+      <c r="D112" t="s">
         <v>61</v>
-      </c>
-      <c r="D112" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C113" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D113" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C114" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D114" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C115" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D115" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C116" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D116" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C117" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D117" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C118" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D118" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C119" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D119" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C120" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D120" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C121" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D121" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C122" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D122" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C123" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D123" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C124" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D124" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="C125" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D125" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C126" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>181</v>
+      </c>
+      <c r="C127" t="s">
         <v>183</v>
       </c>
-      <c r="C127" t="s">
-        <v>185</v>
-      </c>
       <c r="D127" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C128" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D128" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C129" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D129" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C130" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D130" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C131" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D131" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C132" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D132" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C133" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D133" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C134" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D134" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C135" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D135" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C136" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D136" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C137" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D137" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C138" t="s">
+        <v>10</v>
+      </c>
+      <c r="D138" t="s">
         <v>11</v>
-      </c>
-      <c r="D138" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C139" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D139" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C140" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D140" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C141" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D141" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C142" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D142" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C143" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D143" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C144" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D144" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C145" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D145" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C146" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D146" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C147" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D147" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C148" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C149" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D149" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C150" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D150" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C151" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D151" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C152" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152" t="s">
         <v>16</v>
-      </c>
-      <c r="D152" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
         <v>18</v>
-      </c>
-      <c r="D153" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C154" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D154" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C155" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D155" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C156" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D156" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C157" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D157" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C158" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D158" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C159" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D159" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C160" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D160" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C161" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D161" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C162" t="s">
+        <v>25</v>
+      </c>
+      <c r="D162" t="s">
         <v>26</v>
-      </c>
-      <c r="D162" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C163" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D163" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C164" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D164" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C165" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D165" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C166" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D166" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C167" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D167" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C168" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D168" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C169" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D169" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C170" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D170" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C171" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D171" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D172" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C173" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D173" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C174" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D174" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C175" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D175" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C176" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D176" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C177" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D177" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C178" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D178" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C179" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D179" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C180" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D180" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C181" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D181" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C182" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D182" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C183" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D183" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C184" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D184" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C185" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D185" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C186" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D186" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C187" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D187" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C188" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D188" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C189" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D189" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C190" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D190" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C191" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D191" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C192" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D192" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C193" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D193" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C194" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D194" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C195" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D195" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C196" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D196" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C197" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D197" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C198" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D198" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C199" t="s">
+        <v>37</v>
+      </c>
+      <c r="D199" t="s">
         <v>38</v>
-      </c>
-      <c r="D199" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C200" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D200" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C201" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D201" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C202" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D202" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D203" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C204" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D204" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C205" t="s">
+        <v>39</v>
+      </c>
+      <c r="D205" t="s">
         <v>40</v>
-      </c>
-      <c r="D205" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C207" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D207" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C208" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D208" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C209" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C210" t="s">
+        <v>42</v>
+      </c>
+      <c r="D210" t="s">
         <v>43</v>
-      </c>
-      <c r="D210" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D211" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C212" t="s">
+        <v>44</v>
+      </c>
+      <c r="D212" t="s">
         <v>45</v>
-      </c>
-      <c r="D212" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C213" t="s">
+        <v>46</v>
+      </c>
+      <c r="D213" t="s">
         <v>47</v>
-      </c>
-      <c r="D213" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C214" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D214" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C215" t="s">
+        <v>49</v>
+      </c>
+      <c r="D215" t="s">
         <v>50</v>
-      </c>
-      <c r="D215" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C216" t="s">
+        <v>51</v>
+      </c>
+      <c r="D216" t="s">
         <v>52</v>
-      </c>
-      <c r="D216" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C217" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D217" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C218" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D218" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C219" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D219" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C220" t="s">
+        <v>56</v>
+      </c>
+      <c r="D220" t="s">
         <v>57</v>
-      </c>
-      <c r="D220" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C221" t="s">
+        <v>58</v>
+      </c>
+      <c r="D221" t="s">
         <v>59</v>
-      </c>
-      <c r="D221" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C222" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D222" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C223" t="s">
+        <v>60</v>
+      </c>
+      <c r="D223" t="s">
         <v>61</v>
-      </c>
-      <c r="D223" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C224" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D224" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C225" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D225" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C226" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D226" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C227" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D227" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C228" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D228" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C229" t="s">
+        <v>63</v>
+      </c>
+      <c r="D229" t="s">
         <v>64</v>
-      </c>
-      <c r="D229" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C230" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D230" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C231" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D231" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C232" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D232" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C233" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D233" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C234" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D234" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C235" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D235" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C236" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D236" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C237" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D237" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C238" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D238" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C239" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D239" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C240" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D240" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C241" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D241" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C242" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D242" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C243" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D243" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C244" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D244" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C245" t="s">
+        <v>13</v>
+      </c>
+      <c r="D245" t="s">
         <v>14</v>
-      </c>
-      <c r="D245" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>292</v>
+      </c>
+      <c r="C246" t="s">
         <v>294</v>
       </c>
-      <c r="C246" t="s">
-        <v>296</v>
-      </c>
       <c r="D246" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C247" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D247" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C248" t="s">
+        <v>19</v>
+      </c>
+      <c r="D248" t="s">
         <v>20</v>
-      </c>
-      <c r="D248" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C249" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D249" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C250" t="s">
+        <v>22</v>
+      </c>
+      <c r="D250" t="s">
         <v>23</v>
-      </c>
-      <c r="D250" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C251" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D251" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C252" t="s">
+        <v>31</v>
+      </c>
+      <c r="D252" t="s">
         <v>32</v>
-      </c>
-      <c r="D252" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C253" t="s">
+        <v>33</v>
+      </c>
+      <c r="D253" t="s">
         <v>34</v>
-      </c>
-      <c r="D253" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C254" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D254" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C255" t="s">
+        <v>46</v>
+      </c>
+      <c r="D255" t="s">
         <v>47</v>
-      </c>
-      <c r="D255" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C256" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D256" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C257" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D257" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/database_manutenzione.xlsx
+++ b/database_manutenzione.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="865" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1073" uniqueCount="554">
   <si>
     <t>Scadenza</t>
   </si>
@@ -39,30 +39,9 @@
     <t>Struttura cassa</t>
   </si>
   <si>
-    <t>MR1-01A-TC027</t>
-  </si>
-  <si>
     <t>MV005</t>
   </si>
   <si>
-    <t>Musetto mobile Ispezione visiva, pulizia, prova funzionale | S MV-270 MV005</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC024</t>
-  </si>
-  <si>
-    <t>08 10 (in tessuto CSM) __|infiltrazioni, buchi, danneggiamenti s Mv-270 MV005</t>
-  </si>
-  <si>
-    <t>MR1-08A-TC022</t>
-  </si>
-  <si>
-    <t>MR1-01A-TCO11</t>
-  </si>
-  <si>
-    <t>09 10 JDotazioni di bordo attrezzatura s NA NA</t>
-  </si>
-  <si>
     <t>MR1-14A-TC002</t>
   </si>
   <si>
@@ -78,18 +57,12 @@
     <t>MR1-04A-TC016</t>
   </si>
   <si>
-    <t>22 10 chiavi Verifica visiva in opera dell’apparato Ss MV-250 MV006</t>
-  </si>
-  <si>
     <t>MR1-04A-TC034</t>
   </si>
   <si>
     <t>22 20 chiavi Pulizia e lubrificazione S MV-250 | Mv0o06</t>
   </si>
   <si>
-    <t>23 10 rossa Verifica visiva in opera dell’apparato s MV-250 MV006</t>
-  </si>
-  <si>
     <t>MR1-04A-TCO74</t>
   </si>
   <si>
@@ -105,30 +78,18 @@
     <t>(WC)a i Scarico della toilette con acido citrico. ie) N/A N/A</t>
   </si>
   <si>
-    <t>MR1-15A-TC005</t>
-  </si>
-  <si>
     <t>MR1-15A-TC020</t>
   </si>
   <si>
     <t>Lavastoviglie Test funzionale. ie) N/A N/A</t>
   </si>
   <si>
-    <t>08-07 | 05 pneumatico e freno |tenuta della condotta principale (cdp &lt; s Mv-220 Mvoo7</t>
-  </si>
-  <si>
     <t>MR1-03A-TC054</t>
   </si>
   <si>
-    <t>03-03 |10a}Carrello completo |Ispezione visiva organi carrello Ss MV-210 MV003</t>
-  </si>
-  <si>
     <t>MR1-02A-TC001</t>
   </si>
   <si>
-    <t>03-03 |10b}/Carrello completo |Ispezione visiva organi rodiggio Ss MV-200 MV002</t>
-  </si>
-  <si>
     <t>12 10 Laterale Attiva Pulizia radiatore olio c N/A N/A</t>
   </si>
   <si>
@@ -240,105 +201,24 @@
     <t>ian 5 Copiglia ,</t>
   </si>
   <si>
-    <t>Struttura cassa Verifica integrita carenature e finestrini s Mv-270 | MV005</t>
-  </si>
-  <si>
-    <t>Struttura cassa | Controllo eventuale corrosione degli s MV-270 | MVO00S</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC025</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>04 tergilavacristallo | sostituzione spazzola tergicristallo</t>
-  </si>
-  <si>
-    <t>MR1-01A-TCO05</t>
-  </si>
-  <si>
-    <t>Musetto mobile funzionale s MvV-270 | MVO005</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC001</t>
-  </si>
-  <si>
-    <t>03-02-05] 10 aerodinamica Controllo visivo integrita s MV-270 MV005</t>
-  </si>
-  <si>
-    <t>01 , ’ infiltrazioni, buchi, danneggiamenti</t>
-  </si>
-  <si>
-    <t>MR1-08A-TC023</t>
-  </si>
-  <si>
-    <t>01 30 compl. Ispezione visiva per rilevamento perdite | C N/A N/A</t>
-  </si>
-  <si>
-    <t>02 10 collegamento, danneggiamenti, usura dei rivestimenti C N/A N/A</t>
-  </si>
-  <si>
-    <t>04 10 compl. danneggiamenti, usura dei rivestimenti C N/A N/A</t>
-  </si>
-  <si>
-    <t>Molla a balestra Ispezione visiva trimestrale C N/A N/A</t>
-  </si>
-  <si>
-    <t>01 automatico i i</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC012</t>
-  </si>
-  <si>
-    <t>02 10 semipermanente — |risonanza s Mv-240 Mvo04</t>
-  </si>
-  <si>
     <t>MR1-01A-TC015</t>
   </si>
   <si>
-    <t>03 10 recupero Controllo visivo s Mv-240 | MV004</t>
-  </si>
-  <si>
     <t>MR1-01A-TC038</t>
   </si>
   <si>
-    <t>02 intercomunicante |tenute bordi; antina porta; guida</t>
-  </si>
-  <si>
     <t>MR1-08A-TC013</t>
   </si>
   <si>
     <t>04 Gangway tenute bordi; antina porta; guida</t>
   </si>
   <si>
-    <t>Gradino scorrevole|Controllo s Mv-260 | MVO008</t>
-  </si>
-  <si>
     <t>MR1-08A-TC001</t>
   </si>
   <si>
-    <t>og | 10 |Potazioni di bordo |aitrezzatura S | NA NA</t>
-  </si>
-  <si>
-    <t>22 10 chiavi Verifica visiva in opera dell’apparato s MV-250 MVO006</t>
-  </si>
-  <si>
-    <t>22 20 chiavi Pulizia e lubrificazione s MV-250 | MVO006</t>
-  </si>
-  <si>
-    <t>23 10 rossa Verifica visiva in opera dell’apparato s MV-250 MVO006</t>
-  </si>
-  <si>
     <t>MR1-04A-TC074</t>
   </si>
   <si>
-    <t>23 20 rossa Pulizia e lubrificazione s MV-250 | MVO006</t>
-  </si>
-  <si>
-    <t>01 | 10 |interna Pulizia R |" N/A N/A</t>
-  </si>
-  <si>
     <t>MR1-04A-TC001</t>
   </si>
   <si>
@@ -348,159 +228,45 @@
     <t>MR1-04A-TC002</t>
   </si>
   <si>
-    <t>(WC) a i Scarico della toilette con acido citrico C N/A N/A</t>
-  </si>
-  <si>
     <t>MR1-15A-TC012</t>
   </si>
   <si>
-    <t>(WC) a i Scarico della toilette con acido citrico. C N/A N/A</t>
-  </si>
-  <si>
-    <t>Evaporatore Pulizia acqua di scarico C N/A N/A</t>
-  </si>
-  <si>
-    <t>Lavastoviglie Test funzionale. C N/A N/A</t>
-  </si>
-  <si>
-    <t>pneumatico e tenuta della condotta principale (cdp &lt; s MV-220 | Mvo007</t>
-  </si>
-  <si>
     <t>MR1-03A-TC001</t>
   </si>
   <si>
-    <t>FDU Test allarme e verifica LED S _ |ANNESSO- | MV-280 MV009</t>
-  </si>
-  <si>
-    <t>03-03 | 10a |Carrello completo |Ispezione visiva organi carrello s Mv-210 | Mvoo3</t>
-  </si>
-  <si>
-    <t>03-03 | 10b |Carrello completo |Ispezione visiva organi rodiggio s Mv-200 | Mvoo2</t>
-  </si>
-  <si>
-    <t>03-03-02] 10 primaria Ispezione visiva ammortizzatore primario | S MV-210 MV003</t>
-  </si>
-  <si>
     <t>MR1-02A-TC010</t>
   </si>
   <si>
-    <t>03-03-02] 20 primaria Ispezione visiva molle elicoidali s MV-210 MVO003</t>
-  </si>
-  <si>
     <t>MR1-02A-TC015</t>
   </si>
   <si>
-    <t>condaria antiserpeggio s Mv-210 | Mv003</t>
-  </si>
-  <si>
     <t>MR1-02A-TCO11</t>
   </si>
   <si>
-    <t>08-03-03) 30 secondaria pneumatica s MV-210 MV003</t>
-  </si>
-  <si>
     <t>MR1-02A-TC016</t>
   </si>
   <si>
-    <t>03-03-03] 40 secondaria sovrappressione, valvola di livellamento | S Mv-210 | Mvoo3</t>
-  </si>
-  <si>
-    <t>MR1-02A-TCO17</t>
-  </si>
-  <si>
-    <t>03-03-03] 50 secondaria Ispezione visiva barra antirollio s Mv-210 | Mvoo3</t>
-  </si>
-  <si>
     <t>MR1-02A-TC018</t>
   </si>
   <si>
-    <t>03-03-03| 60 secondaria Ispezione visiva fine corsa laterale s MV-210 | Mvoo3</t>
-  </si>
-  <si>
     <t>MR1-02A-TC014</t>
   </si>
   <si>
     <t>MR1-02A-TC007</t>
   </si>
   <si>
-    <t>12 20 Laterale Attiva Controllo livello olio s MV-210 | MV003</t>
-  </si>
-  <si>
-    <t>MR1-02A-TC006</t>
-  </si>
-  <si>
-    <t>Sala montata Ispezione visiva s MV-200 | Mvoo2</t>
-  </si>
-  <si>
-    <t>Sala montata Regolazione antenna e ugello ungibordo s Mv-200 | Mvoo2</t>
-  </si>
-  <si>
     <t>MR1-02A-TC003</t>
   </si>
   <si>
-    <t>Sala montata Ispezione visiva boccole e coperchi s Mv-200 | MV002</t>
-  </si>
-  <si>
     <t>MR1-02A-TC005</t>
   </si>
   <si>
-    <t>trazione trazione s Mv-210 | MV003</t>
-  </si>
-  <si>
     <t>MR1-02A-TC020</t>
   </si>
   <si>
-    <t>Cacciapietre lanciasabbia e collegamenti s MV-210 Mvo03</t>
-  </si>
-  <si>
-    <t>Impianto elettrico |Ispezione visiva s MV-210 MVO003</t>
-  </si>
-  <si>
-    <t>09 20 a terra Ispezione visiva s MV-210 MVO003</t>
-  </si>
-  <si>
-    <t>MR1-02A-TC021</t>
-  </si>
-  <si>
-    <t>messa a terra della]|Ispezione visiva s MV-200 MV002</t>
-  </si>
-  <si>
-    <t>10 10 tappi Ispezione visiva s MV-210 MVO003</t>
-  </si>
-  <si>
     <t>MR1-02A-TC028</t>
   </si>
   <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>02 ungibordo rabbocco</t>
-  </si>
-  <si>
-    <t>02 ungibordo Controllo della spruzzata e di tenuta</t>
-  </si>
-  <si>
-    <t>02 30 ungibordo Controllo regolazione ugello R N/A N/A</t>
-  </si>
-  <si>
-    <t>Riduttore Verifica livello e aspetto dell'olio s MV-200 MV002</t>
-  </si>
-  <si>
-    <t>Riduttore dentata e asta di reazione s Mv-200 | Mvoo2</t>
-  </si>
-  <si>
-    <t>05 10 leve lubrificazione timoneria, controllo Ss MV-220 MV007</t>
-  </si>
-  <si>
-    <t>06 10 parcheggio a funzionale del sistema di rilascio, s MV-220 Mv007</t>
-  </si>
-  <si>
-    <t>01 20 ruota (pos.14.09) |Controllo condotti raffreddamento e s MV-200 MV002</t>
-  </si>
-  <si>
-    <t>01 30 ruota (pos.14.09) |superfici di attrito s MV-200 MV002</t>
-  </si>
-  <si>
     <t>MR1-03A-TC041</t>
   </si>
   <si>
@@ -510,111 +276,24 @@
     <t>MR1-03A-TC046</t>
   </si>
   <si>
-    <t>28 10 pantografo CC RS ispezione visiva, pulizia e ingrassaggio s MV-250 MVO006</t>
-  </si>
-  <si>
     <t>MR1-04A-TC022</t>
   </si>
   <si>
-    <t>08-04-02) 10 principale Controllo ed eventuale sostituzione s MV-250 | MVO006</t>
-  </si>
-  <si>
-    <t>Motore di trazione |Ispezione visiva R N/A N/A</t>
-  </si>
-  <si>
     <t>03 motore di trazione |G2</t>
   </si>
   <si>
     <t>MR1-04A-TC039</t>
   </si>
   <si>
-    <t>pneumatica 7016</t>
-  </si>
-  <si>
-    <t>Ispezione visiva cacciapietre,</t>
-  </si>
-  <si>
-    <t>Sospensione secondaria Sospensione secondaria Ceplattyn ECO 300 5003009823</t>
-  </si>
-  <si>
     <t>Ispezione visiva</t>
   </si>
   <si>
-    <t>Salamontata eventuale riprofilatura )ETR1 000-V300ZEFIRO-|Calipri - Tool misura</t>
-  </si>
-  <si>
     <t>MR1-02A-</t>
   </si>
   <si>
-    <t>Dispositivo di ETR1000-V300ZEFIRO-,</t>
-  </si>
-  <si>
-    <t>MR1-02A</t>
-  </si>
-  <si>
-    <t>03-07-0201 |30 Disco freno su scheggiature su ETR1000-V300ZEFIRO-: Calipri Dispositivo di</t>
-  </si>
-  <si>
     <t>MR1-03A</t>
   </si>
   <si>
-    <t>03-07-02-02 |30 |assile scheggiature su ETR1000-V300ZEFIRO-| Calipri - Dispositivo di</t>
-  </si>
-  <si>
-    <t>MR1-03A-</t>
-  </si>
-  <si>
-    <t>F3_rev16</t>
-  </si>
-  <si>
-    <t>Struttura cassa Verifica integrita carenature e finestrini s Mv-270 | MVO00S</t>
-  </si>
-  <si>
-    <t>Struttura cassa Controllo eventuale corrosione degli s Mv-270 | MV005</t>
-  </si>
-  <si>
-    <t>04 tergilavacristallo spazzola tergicristallo</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC005</t>
-  </si>
-  <si>
-    <t>03-02-05} 10 aerodinamica Controllo visivo integrita Ss MV-270 MV005</t>
-  </si>
-  <si>
-    <t>Carenature inferiori corrosione. S MV-270 | MV005</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC042</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>MR1-01A-TC040</t>
-  </si>
-  <si>
-    <t>01 . pr infiltrazioni, buchi, danneggiamenti</t>
-  </si>
-  <si>
-    <t>01 30 compl. Ispezione visiva per rilevamento perdite ie) N/A N/A</t>
-  </si>
-  <si>
-    <t>02 collegamento, lanneggiamenti, usura dei rivestimenti</t>
-  </si>
-  <si>
-    <t>04 10 compl. danneggiamenti, usura dei rivestimenti ie) N/A N/A</t>
-  </si>
-  <si>
-    <t>Molla a balestra Ispezione visiva trimestrale c N/A N/A</t>
-  </si>
-  <si>
-    <t>01 10 automatico lubrificazione s Mv-240 | Mv004</t>
-  </si>
-  <si>
-    <t>01 automatico i i i i</t>
-  </si>
-  <si>
     <t>02 10 semipermanente |risonanza s MV-240 Mvo04</t>
   </si>
   <si>
@@ -895,33 +574,6 @@
   </si>
   <si>
     <t>Disco freno su ruota | SPezione usura disco è | -T4 999.v300ZEFIRO-,|Calipri - Dispositivo di</t>
-  </si>
-  <si>
-    <t>I0_rev16</t>
-  </si>
-  <si>
-    <t>Struttura cassa Verifica integrita carenature e finestrini s Mv-270 MV005</t>
-  </si>
-  <si>
-    <t>02 20 41.05 3kV carbonio e dell'usura dell'archetto. s MV-250 MV006</t>
-  </si>
-  <si>
-    <t>02 40 62.05 25kV carbonio e dell'usura dell'archetto. s MV-250 MV006</t>
-  </si>
-  <si>
-    <t>22 20 chiavi Pulizia e lubrificazione S MV-250 MV006</t>
-  </si>
-  <si>
-    <t>23 20 rossa Pulizia e lubrificazione S MV-250 MV006</t>
-  </si>
-  <si>
-    <t>MR1-02A-TCO01</t>
-  </si>
-  <si>
-    <t>03-05-05 | 10 |Riduttore Verifica livello e aspetto dell'olio Ss MV-200 MV002</t>
-  </si>
-  <si>
-    <t>FDU Test allarme e verifica LED S |ANNESSO- MV-280 MV009</t>
   </si>
   <si>
     <t>Ispezione visiva, pulizia, prova funzionale</t>
@@ -1338,13 +990,2759 @@
   </si>
   <si>
     <t>F2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Struttura cassa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dotazioni di bordo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Pantografo WBL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>41.05 3kV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Pantografo WBL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>62.05 25kV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scambiatore di chiavi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pannello chiave rossa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Impianto pneumatico e freno</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Carrello completo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Impianto ungibordo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Riduttore</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>FDU</t>
+    </r>
+  </si>
+  <si>
+    <t>I0</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica presenza e leggibilità dei pittogrammi ed eventuale ripristino Verifica integrità carenature e finestrini Verifica esterno cassa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo integrità e presenza attrezzatura</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione e verifica dello spessore minimo residuo dello strisciante in carbonio e dell'usura dell'archetto. Eventuale sostituzione dello strisciante</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica visiva in opera dell’apparato</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia e lubrificazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Test completo del freno comandato da IDU
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Effettuare il test di performance dei compressori principali e la prova di tenuta della condotta principale (cdp &lt; 0,5 bar in 3 minuti, con impianti Toilet ed HVAC isolati), eliminando eventuali perdite sui componenti pneumatici.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva organi carrello</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva organi rodiggio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo livello olio ed eventuale rabbocco</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica livello e aspetto dell'olio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test allarme e verifica LED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-01A-TC027</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-14A-TC002</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-04A-TC010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-04A-TC016</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-04A-TC034</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-04A-TC074</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-03A-TC054</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-02A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-02A-TC023</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO- MR1-02A-TC026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEF. ANNESSO- MR1-01A- TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV005</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>N/A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV006</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV003</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV002</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial MT"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV009</t>
+    </r>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Ispezione visiva organi carrello e rodiggio</t>
+  </si>
+  <si>
+    <t>Sostituzione olio</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Struttura cassa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Impianto tergilavacristallo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Musetto mobile</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Testata aerodinamica</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Doppio soffietto ondulato, compl. (in materiale CSM)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Struttura doppia, compl.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ponte di collegamento,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>compl. con slitta</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Copertura ponte, compl.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Molla a balestra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Carenatura, compl. (in tessuto CSM)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Accoppiatore automatico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Accoppiatore semipermanente</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Maschera di recupero</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica presenza e leggibilità dei pittogrammi ed eventuale ripristino Verifica integrità carenature e finestrini Verifica esterno cassa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo fissaggio apparati del sottocassa
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo eventuale corrosione degli
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>elementi di fissaggio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo ed eventuale sostituzione spazzola tergicristallo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva, pulizia, prova funzionale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo integrità</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva per rilevamento infiltrazioni, buchi, danneggiamenti</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva per rilevamento perdite</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ispezione visiva per rilevamento danneggiamenti, usura dei rivestimenti
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>antiscivolo, etc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ispezione visiva per rilevamento
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>danneggiamenti, usura dei rivestimenti antiscivolo, etc.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva trimestrale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo e funzionale, pulizia e lubrificazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo inclinazione. Riparazione protezione anticorrosiva piastra frontale e dei coni maschio e femmina. Pulizia e ingrassaggio asta del pistone e guide coperchio scatola portacontatti</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo e pulizia. Test di risonanza</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC027</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC025</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC005</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC024</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-08A-TC023</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-08A-TC022</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC011</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC012</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC015</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-01A-TC038</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV005</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N/A</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV004</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Porte intercomunicante</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Porta Bistrò - Gangway</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia &amp; Controllo di fusibile incendio; operatore sbloccaggio ; microswitch; set tenute bordi; antina porta; guida pavimento</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia &amp; Controllo  di fusibile incendio; operatore sbloccaggio ; microswitch; set tenute bordi; antina porta; guida pavimento</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-08A-TC013</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Porta passeggeri Sx/Dx
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e gradino</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo di sicurezza come da Checklist di Sicurezza  DDEDE10394E36</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Gradino scorrevole</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-08A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV008</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Porta PMR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dotazioni di bordo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Pantografo WBL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>41.05 3kV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Pantografo WBL
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>62.05 25kV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scambiatore di chiavi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pannello chiave rossa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Illuminazione interna</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Illuminazione
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>interna di emergenza</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Sistema toilette (WC) a
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>depressione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Evaporatore</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Lavastoviglie</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Impianto pneumatico e freno</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Filtro di aspirazione
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Pos.13.18)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FDU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Carrello completo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sospensione primaria</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sospensione secondaria</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sospensione Laterale Attiva</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sala montata</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Collegamento di trazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cacciapietre</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Impianto elettrico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Set cavi di messa a terra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Dispositivo di messa a terra della
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>boccola</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Tubi flessibili e tappi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Supporti elastici motore di trazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ammortizzatore laterale motore</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Rilevatore temperatura boccole (RTB)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Impianto ungibordo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Riduttore</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cilindri freno tipo C3 con gruppo leve
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(pos. 14.01, 14.10)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Gruppo freno tipo C3
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(freno di parcheggio a molla)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(pos. 14.13, 14.15)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Disco freno su ruota (pos.14.09)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Disco freno su assile (pos.14.03,14.04)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sezionatore e messa a terra pantografo CC RS 25.20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trasformatore principale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Motore di trazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Motoventilatore motore di trazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo visivo integrità e presenza attrezzatura</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione e verifica dello spessore minimo residuo dello strisciante in carbonio e dell'usura dell'archetto. Eventuale sostituzione dello strisciante</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica visiva in opera dell’apparato</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia e lubrificazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scarico della toilette con acido citrico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Scarico della toilette con acido citrico.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia acqua di scarico</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test funzionale.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Test completo del freno comandato da IDU
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Effettuare il test di performance dei compressori principali e la prova di tenuta della condotta principale (cdp &lt; 0,5 bar in 3 minuti, con impianti Toilet ed HVAC isolati), eliminando eventuali perdite sui componenti pneumatici.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia e controllo intasamento</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Test allarme e verifica LED</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva organi carrello</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva organi rodiggio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva ammortizzatore primario</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva molle elicoidali</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva ammortizzatore antiserpeggio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva sospensione pneumatica</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva valvola di sovrappressione, valvola di livellamento e asta di controllo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva barra antirollio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva fine corsa laterale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Pulizia radiatore olio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva Controllo livello olio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo profilo ruote monoblocco ed eventuale riprofilatura
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Regolazione antenna e ugello ungibordo
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>dopo riprofilatura ruote</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva boccole e coperchi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva gruppo collegamento di trazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva cacciapietre, staffa lanciasabbia e collegamenti</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione accurata</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo livello olio ed eventuale rabbocco</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Test di funzionamento
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo della spruzzata e di tenuta</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo regolazione ugello</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica livello e aspetto dell'olio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Verifica visiva del riduttore, della coppia dentata e asta di reazione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo stato unità di frenatura, controllo gioco pastiglie/dischi, eventuale lubrificazione timoneria, controllo consumo guarnizioni ed eventuale sostituzione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo stato unità di frenatura, controllo gioco pastiglie/dischi, eventuale lubrificazione timoneria, verifica funzionale del sistema di rilascio, controllo consumo guarnizioni ed eventuale sostituzione</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva e funzionale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo assenza crepe, fessurazioni, bruciature sul disco
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo condotti raffreddamento e
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>assenza crepe</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione usura disco e scheggiature su superfici di attrito</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo funzionale
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ispezione visiva, pulizia e ingrassaggio coltello</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ispezione visiva griglie uscita aria e scambiatore di calore.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Controllo ed eventuale sostituzione
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Silicagel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo ed eventuale sostituzione filtro G2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-08A-TC007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-14A-TC002</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC016</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC034</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC074</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC002</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-15A-TC005</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-15A-TC012</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-15A-TC020</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC054</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ETR1000-V300ZEF. ANNESSO- MR1-01A-
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC010</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC015</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC011</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC016</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC017</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC018</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC014</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC006</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC008 MR1-02A-TC033</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC003</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC005</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC020</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC013</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC030</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC021</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC028</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC019</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC012</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC029</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC023</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC024</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC022</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-02A-TC032</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC032</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC035</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC039</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC040</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC041</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC044</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC045</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-03A-TC046</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC022</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC038</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-07A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ETR1000-V300ZEFIRO-MR1-04A-TC039</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV006</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV009</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV003</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MV002</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ispezione visiva organi carrello e rodigio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Ispezione visiva cacciapietre,
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>staffa lanciasabbia e collegamenti</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-02A-TC001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-02A-TC014</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-02A-TC015 MR1-02A-TC016 MR1-02A-TC014 MR1-02A-TC005 MR1-02A-TC013</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dispositivo di messa a terra della boccola</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Essicatore aria trasformatore principale</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cilindri freno tipo C3 con gruppo leve, gruppo freno tipo C3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sezionatore e messa a terra CC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo funzionale ispezione visiva, pulizia e ingrassaggio coltello</t>
+    </r>
+  </si>
+  <si>
+    <t>Controllo e lubrificazione // Controllo ed eventuale sostutuzione pastiglie freno</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Controllo ed eventuale sostituzione Silicagel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-02A-TC021</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-02A-TC023</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-02A-TC026</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-04A-TC038 MR1-04A-TC061</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-03A-TC032 MR1-03A-TC035</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-04A-TC022</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>MR1-04A-TC039</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1391,6 +3789,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial MT"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial MT"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1400,7 +3816,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1434,12 +3850,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1487,6 +3927,53 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1791,12 +4278,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F257"/>
+  <dimension ref="A1:F260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="133" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="88.28515625" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="56.85546875" bestFit="1" customWidth="1"/>
@@ -1819,3098 +4306,3729 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>302</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>344</v>
+        <v>228</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>379</v>
+        <v>263</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>303</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>369</v>
+        <v>253</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>301</v>
+        <v>185</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>380</v>
+        <v>264</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>304</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>370</v>
+        <v>254</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>345</v>
+        <v>229</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>381</v>
+        <v>265</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>305</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>371</v>
+        <v>255</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>306</v>
+        <v>190</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>382</v>
+        <v>266</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>318</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>308</v>
+        <v>192</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>309</v>
+        <v>193</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>383</v>
+        <v>267</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>310</v>
+        <v>194</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>319</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>311</v>
+        <v>195</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>314</v>
+        <v>198</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>384</v>
+        <v>268</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>372</v>
+        <v>256</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>315</v>
+        <v>199</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>385</v>
+        <v>269</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>320</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>373</v>
+        <v>257</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>315</v>
+        <v>199</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>386</v>
+        <v>270</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>321</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>313</v>
+        <v>197</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>316</v>
+        <v>200</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>387</v>
+        <v>271</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>313</v>
+        <v>197</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>317</v>
+        <v>201</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>387</v>
+        <v>271</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>322</v>
+        <v>206</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>316</v>
+        <v>200</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>388</v>
+        <v>272</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
       <c r="F12" s="4"/>
     </row>
     <row r="13" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>322</v>
+        <v>206</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>317</v>
+        <v>201</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>388</v>
+        <v>272</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>346</v>
+        <v>230</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>389</v>
+        <v>273</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>346</v>
+        <v>230</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>342</v>
+        <v>226</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>347</v>
+        <v>231</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>389</v>
+        <v>273</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>323</v>
+        <v>207</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>348</v>
+        <v>232</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>391</v>
+        <v>275</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>324</v>
+        <v>208</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>349</v>
+        <v>233</v>
       </c>
       <c r="D18" s="14" t="s">
-        <v>391</v>
+        <v>275</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>325</v>
+        <v>209</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>365</v>
+        <v>249</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>392</v>
+        <v>276</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>375</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>326</v>
+        <v>210</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>350</v>
+        <v>234</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>393</v>
+        <v>277</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>326</v>
+        <v>210</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>351</v>
+        <v>235</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>393</v>
+        <v>277</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>327</v>
+        <v>211</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>352</v>
+        <v>236</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>394</v>
+        <v>278</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>328</v>
+        <v>212</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>353</v>
+        <v>237</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>395</v>
+        <v>279</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>329</v>
+        <v>213</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>354</v>
+        <v>238</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>396</v>
+        <v>280</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>330</v>
+        <v>214</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>397</v>
+        <v>281</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>331</v>
+        <v>215</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>355</v>
+        <v>239</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>398</v>
+        <v>282</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>332</v>
+        <v>216</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>399</v>
+        <v>283</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>333</v>
+        <v>217</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>356</v>
+        <v>240</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>400</v>
+        <v>284</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>334</v>
+        <v>218</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>401</v>
+        <v>285</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>376</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>335</v>
+        <v>219</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>357</v>
+        <v>241</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>402</v>
+        <v>286</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>335</v>
+        <v>219</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>366</v>
+        <v>250</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>403</v>
+        <v>287</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>335</v>
+        <v>219</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>358</v>
+        <v>242</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>404</v>
+        <v>288</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>359</v>
+        <v>243</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>405</v>
+        <v>289</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>336</v>
+        <v>220</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>360</v>
+        <v>244</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>406</v>
+        <v>290</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>374</v>
+        <v>258</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>361</v>
+        <v>245</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>407</v>
+        <v>291</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>375</v>
+        <v>259</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>343</v>
+        <v>227</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>362</v>
+        <v>246</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>408</v>
+        <v>292</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>375</v>
+        <v>259</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>337</v>
+        <v>221</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>409</v>
+        <v>293</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>337</v>
+        <v>221</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>410</v>
+        <v>294</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>338</v>
+        <v>222</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>363</v>
+        <v>247</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>411</v>
+        <v>295</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>338</v>
+        <v>222</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>367</v>
+        <v>251</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>412</v>
+        <v>296</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>377</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>339</v>
+        <v>223</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>368</v>
+        <v>252</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>413</v>
+        <v>297</v>
       </c>
       <c r="E41" s="13" t="s">
-        <v>307</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>340</v>
+        <v>224</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>414</v>
+        <v>298</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>312</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>341</v>
+        <v>225</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>364</v>
+        <v>248</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>415</v>
+        <v>299</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>378</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="C45" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D45" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="C46" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>416</v>
+        <v>300</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>300</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
+      <c r="D48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C49" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>301</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>359</v>
+      </c>
+      <c r="D50" s="28" t="s">
+        <v>373</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="C51" s="29" t="s">
+        <v>360</v>
+      </c>
+      <c r="D51" s="28" t="s">
+        <v>374</v>
+      </c>
+      <c r="E51" s="28" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>301</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>347</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>361</v>
+      </c>
+      <c r="D52" s="28" t="s">
+        <v>375</v>
+      </c>
+      <c r="E52" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="C53" s="28" t="s">
+        <v>362</v>
+      </c>
+      <c r="D53" s="28" t="s">
+        <v>376</v>
+      </c>
+      <c r="E53" s="28" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>301</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="C54" s="28" t="s">
+        <v>363</v>
+      </c>
+      <c r="D54" s="28" t="s">
+        <v>377</v>
+      </c>
+      <c r="E54" s="28" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>301</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>350</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D55" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="E55" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>301</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>351</v>
+      </c>
+      <c r="C56" s="28" t="s">
+        <v>365</v>
+      </c>
+      <c r="D56" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>301</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="C57" s="29" t="s">
+        <v>366</v>
+      </c>
+      <c r="D57" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>301</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="C58" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="E58" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>301</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="C59" s="28" t="s">
+        <v>368</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>378</v>
+      </c>
+      <c r="E59" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="C60" s="28" t="s">
+        <v>364</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>379</v>
+      </c>
+      <c r="E60" s="28" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>301</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="C61" s="28" t="s">
+        <v>369</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>380</v>
+      </c>
+      <c r="E61" s="28" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>301</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="C62" s="28" t="s">
+        <v>370</v>
+      </c>
+      <c r="D62" s="28" t="s">
+        <v>381</v>
+      </c>
+      <c r="E62" s="28" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>301</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="C63" s="28" t="s">
+        <v>371</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>382</v>
+      </c>
+      <c r="E63" s="28" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>301</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" s="28" t="s">
+        <v>372</v>
+      </c>
+      <c r="D64" s="28" t="s">
+        <v>383</v>
+      </c>
+      <c r="E64" s="28" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="C65" s="28" t="s">
+        <v>389</v>
+      </c>
+      <c r="D65" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="E65" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="C66" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="D66" s="28" t="s">
+        <v>391</v>
+      </c>
+      <c r="E66" s="28" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>392</v>
+      </c>
+      <c r="C67" s="28" t="s">
+        <v>393</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="E67" s="28" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>301</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="C68" s="28" t="s">
+        <v>395</v>
+      </c>
+      <c r="D68" s="28" t="s">
+        <v>396</v>
+      </c>
+      <c r="E68" s="28" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>398</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="D69" s="26" t="s">
+        <v>478</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>301</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="D70" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="E70" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="27" t="s">
+        <v>400</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>437</v>
+      </c>
+      <c r="D71" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="E71" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>301</v>
+      </c>
+      <c r="B72" s="27" t="s">
+        <v>401</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>437</v>
+      </c>
+      <c r="D72" s="26" t="s">
+        <v>481</v>
+      </c>
+      <c r="E72" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>301</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="D73" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="E73" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>301</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="D74" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="E74" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>301</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>438</v>
+      </c>
+      <c r="D75" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="E75" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="C76" s="30" t="s">
+        <v>439</v>
+      </c>
+      <c r="D76" s="26" t="s">
+        <v>483</v>
+      </c>
+      <c r="E76" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="C77" s="30" t="s">
+        <v>440</v>
+      </c>
+      <c r="D77" s="26" t="s">
+        <v>484</v>
+      </c>
+      <c r="E77" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>301</v>
+      </c>
+      <c r="B78" s="27" t="s">
+        <v>405</v>
+      </c>
+      <c r="C78" s="30" t="s">
+        <v>440</v>
+      </c>
+      <c r="D78" s="26" t="s">
+        <v>485</v>
+      </c>
+      <c r="E78" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>301</v>
+      </c>
+      <c r="B79" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="D79" s="26" t="s">
+        <v>486</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>487</v>
+      </c>
+      <c r="E80" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>301</v>
+      </c>
+      <c r="B81" s="27" t="s">
+        <v>406</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>442</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>486</v>
+      </c>
+      <c r="E81" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>301</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>407</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>443</v>
+      </c>
+      <c r="D82" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="E82" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>301</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="C83" s="30" t="s">
+        <v>444</v>
+      </c>
+      <c r="D83" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="E83" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>301</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>409</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>445</v>
+      </c>
+      <c r="D84" s="26" t="s">
+        <v>489</v>
+      </c>
+      <c r="E84" s="30" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>301</v>
+      </c>
+      <c r="B85" s="27" t="s">
+        <v>410</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>446</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>490</v>
+      </c>
+      <c r="E85" s="30" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>301</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="C86" s="30" t="s">
+        <v>447</v>
+      </c>
+      <c r="D86" s="27" t="s">
+        <v>491</v>
+      </c>
+      <c r="E86" s="30" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>301</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="C87" s="30" t="s">
+        <v>448</v>
+      </c>
+      <c r="D87" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="E87" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>301</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="D88" s="26" t="s">
+        <v>492</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>301</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C89" s="30" t="s">
+        <v>450</v>
+      </c>
+      <c r="D89" s="26" t="s">
+        <v>493</v>
+      </c>
+      <c r="E89" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>301</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="D90" s="26" t="s">
+        <v>494</v>
+      </c>
+      <c r="E90" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>301</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C91" s="30" t="s">
+        <v>452</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="E91" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>301</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C92" s="30" t="s">
+        <v>453</v>
+      </c>
+      <c r="D92" s="26" t="s">
+        <v>496</v>
+      </c>
+      <c r="E92" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>301</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C93" s="30" t="s">
+        <v>454</v>
+      </c>
+      <c r="D93" s="26" t="s">
+        <v>497</v>
+      </c>
+      <c r="E93" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>301</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>455</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>498</v>
+      </c>
+      <c r="E94" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>301</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C95" s="30" t="s">
+        <v>456</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>499</v>
+      </c>
+      <c r="E95" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>301</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="C96" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="D96" s="26" t="s">
+        <v>500</v>
+      </c>
+      <c r="E96" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>301</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="C97" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="D97" s="26" t="s">
+        <v>501</v>
+      </c>
+      <c r="E97" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>301</v>
+      </c>
+      <c r="B98" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="C48" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+      <c r="C98" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D98" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="E98" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>301</v>
+      </c>
+      <c r="B99" s="26" t="s">
         <v>416</v>
       </c>
-      <c r="C49" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="C99" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="D99" s="26" t="s">
+        <v>503</v>
+      </c>
+      <c r="E99" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>301</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="C100" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="D100" s="26" t="s">
+        <v>504</v>
+      </c>
+      <c r="E100" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>301</v>
+      </c>
+      <c r="B101" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="C50" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>417</v>
-      </c>
-      <c r="C51" t="s">
-        <v>74</v>
-      </c>
-      <c r="D51" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>417</v>
-      </c>
-      <c r="C52" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>417</v>
-      </c>
-      <c r="C53" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>417</v>
-      </c>
-      <c r="C54" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>417</v>
-      </c>
-      <c r="C55" t="s">
-        <v>82</v>
-      </c>
-      <c r="D55" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>417</v>
-      </c>
-      <c r="C56" t="s">
-        <v>84</v>
-      </c>
-      <c r="D56" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>417</v>
-      </c>
-      <c r="C57" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>417</v>
-      </c>
-      <c r="C58" t="s">
-        <v>86</v>
-      </c>
-      <c r="D58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>417</v>
-      </c>
-      <c r="C59" t="s">
-        <v>87</v>
-      </c>
-      <c r="D59" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>417</v>
-      </c>
-      <c r="C60" t="s">
-        <v>88</v>
-      </c>
-      <c r="D60" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>417</v>
-      </c>
-      <c r="C61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D61" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>417</v>
-      </c>
-      <c r="C62" t="s">
-        <v>92</v>
-      </c>
-      <c r="D62" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>417</v>
-      </c>
-      <c r="C63" t="s">
-        <v>94</v>
-      </c>
-      <c r="D63" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>417</v>
-      </c>
-      <c r="C64" t="s">
-        <v>96</v>
-      </c>
-      <c r="D64" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>417</v>
-      </c>
-      <c r="C65" t="s">
-        <v>97</v>
-      </c>
-      <c r="D65" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>417</v>
-      </c>
-      <c r="C66" t="s">
-        <v>99</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>417</v>
-      </c>
-      <c r="C67" t="s">
-        <v>100</v>
-      </c>
-      <c r="D67" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>417</v>
-      </c>
-      <c r="C68" t="s">
-        <v>101</v>
-      </c>
-      <c r="D68" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>417</v>
-      </c>
-      <c r="C69" t="s">
-        <v>102</v>
-      </c>
-      <c r="D69" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>417</v>
-      </c>
-      <c r="C70" t="s">
-        <v>104</v>
-      </c>
-      <c r="D70" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>417</v>
-      </c>
-      <c r="C71" t="s">
-        <v>105</v>
-      </c>
-      <c r="D71" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>417</v>
-      </c>
-      <c r="C72" t="s">
-        <v>107</v>
-      </c>
-      <c r="D72" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>417</v>
-      </c>
-      <c r="C73" t="s">
-        <v>109</v>
-      </c>
-      <c r="D73" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>417</v>
-      </c>
-      <c r="C74" t="s">
-        <v>109</v>
-      </c>
-      <c r="D74" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>417</v>
-      </c>
-      <c r="C75" t="s">
-        <v>111</v>
-      </c>
-      <c r="D75" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>417</v>
-      </c>
-      <c r="C76" t="s">
-        <v>112</v>
-      </c>
-      <c r="D76" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>417</v>
-      </c>
-      <c r="C77" t="s">
-        <v>113</v>
-      </c>
-      <c r="D77" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>417</v>
-      </c>
-      <c r="C78" t="s">
-        <v>114</v>
-      </c>
-      <c r="D78" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>417</v>
-      </c>
-      <c r="C79" t="s">
-        <v>76</v>
-      </c>
-      <c r="D79" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>417</v>
-      </c>
-      <c r="C80" t="s">
-        <v>116</v>
-      </c>
-      <c r="D80" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>417</v>
-      </c>
-      <c r="C81" t="s">
-        <v>117</v>
-      </c>
-      <c r="D81" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>417</v>
-      </c>
-      <c r="C82" t="s">
-        <v>118</v>
-      </c>
-      <c r="D82" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>417</v>
-      </c>
-      <c r="C83" t="s">
-        <v>119</v>
-      </c>
-      <c r="D83" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>417</v>
-      </c>
-      <c r="C84" t="s">
-        <v>121</v>
-      </c>
-      <c r="D84" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>417</v>
-      </c>
-      <c r="C85" t="s">
-        <v>123</v>
-      </c>
-      <c r="D85" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>417</v>
-      </c>
-      <c r="C86" t="s">
-        <v>125</v>
-      </c>
-      <c r="D86" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>417</v>
-      </c>
-      <c r="C87" t="s">
-        <v>127</v>
-      </c>
-      <c r="D87" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>417</v>
-      </c>
-      <c r="C88" t="s">
-        <v>129</v>
-      </c>
-      <c r="D88" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>417</v>
-      </c>
-      <c r="C89" t="s">
-        <v>131</v>
-      </c>
-      <c r="D89" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>417</v>
-      </c>
-      <c r="C91" t="s">
-        <v>134</v>
-      </c>
-      <c r="D91" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>417</v>
-      </c>
-      <c r="C92" t="s">
-        <v>136</v>
-      </c>
-      <c r="D92" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>417</v>
-      </c>
-      <c r="C93" t="s">
-        <v>137</v>
-      </c>
-      <c r="D93" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>417</v>
-      </c>
-      <c r="C94" t="s">
-        <v>139</v>
-      </c>
-      <c r="D94" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>417</v>
-      </c>
-      <c r="C95" t="s">
-        <v>141</v>
-      </c>
-      <c r="D95" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>417</v>
-      </c>
-      <c r="C96" t="s">
-        <v>143</v>
-      </c>
-      <c r="D96" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>417</v>
-      </c>
-      <c r="C97" t="s">
-        <v>144</v>
-      </c>
-      <c r="D97" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>417</v>
-      </c>
-      <c r="C98" t="s">
-        <v>145</v>
-      </c>
-      <c r="D98" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>417</v>
-      </c>
-      <c r="C99" t="s">
-        <v>147</v>
-      </c>
-      <c r="D99" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>417</v>
-      </c>
-      <c r="C100" t="s">
-        <v>148</v>
-      </c>
-      <c r="D100" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>417</v>
-      </c>
-      <c r="C101" t="s">
-        <v>150</v>
-      </c>
-      <c r="D101" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C101" s="30" t="s">
+        <v>462</v>
+      </c>
+      <c r="D101" s="26" t="s">
+        <v>505</v>
+      </c>
+      <c r="E101" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>417</v>
-      </c>
-      <c r="C102" t="s">
-        <v>151</v>
-      </c>
-      <c r="D102" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="C102" s="30" t="s">
+        <v>463</v>
+      </c>
+      <c r="D102" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="E102" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>417</v>
-      </c>
-      <c r="C103" t="s">
-        <v>152</v>
-      </c>
-      <c r="D103" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="C103" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D103" s="26" t="s">
+        <v>507</v>
+      </c>
+      <c r="E103" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>417</v>
-      </c>
-      <c r="C104" t="s">
-        <v>153</v>
-      </c>
-      <c r="D104" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="C104" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D104" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="E104" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>417</v>
-      </c>
-      <c r="C105" t="s">
-        <v>154</v>
-      </c>
-      <c r="D105" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B105" s="27" t="s">
+        <v>421</v>
+      </c>
+      <c r="C105" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D105" s="26" t="s">
+        <v>508</v>
+      </c>
+      <c r="E105" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>417</v>
-      </c>
-      <c r="C106" t="s">
-        <v>155</v>
-      </c>
-      <c r="D106" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="C106" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D106" s="26" t="s">
+        <v>509</v>
+      </c>
+      <c r="E106" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>417</v>
-      </c>
-      <c r="C107" t="s">
-        <v>156</v>
-      </c>
-      <c r="D107" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>423</v>
+      </c>
+      <c r="C107" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>510</v>
+      </c>
+      <c r="E107" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>417</v>
-      </c>
-      <c r="C108" t="s">
-        <v>157</v>
-      </c>
-      <c r="D108" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="C108" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D108" s="26" t="s">
+        <v>511</v>
+      </c>
+      <c r="E108" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>417</v>
-      </c>
-      <c r="C109" t="s">
-        <v>56</v>
-      </c>
-      <c r="D109" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>425</v>
+      </c>
+      <c r="C109" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D109" s="26" t="s">
+        <v>512</v>
+      </c>
+      <c r="E109" s="30" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>417</v>
-      </c>
-      <c r="C110" t="s">
-        <v>158</v>
-      </c>
-      <c r="D110" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="C110" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D110" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="E110" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>417</v>
-      </c>
-      <c r="C111" t="s">
-        <v>159</v>
-      </c>
-      <c r="D111" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="C111" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="D111" s="26" t="s">
+        <v>514</v>
+      </c>
+      <c r="E111" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>417</v>
-      </c>
-      <c r="C112" t="s">
-        <v>60</v>
-      </c>
-      <c r="D112" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="C112" s="30" t="s">
+        <v>467</v>
+      </c>
+      <c r="D112" s="26" t="s">
+        <v>515</v>
+      </c>
+      <c r="E112" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>417</v>
-      </c>
-      <c r="C113" t="s">
-        <v>161</v>
-      </c>
-      <c r="D113" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="C113" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="D113" s="26" t="s">
+        <v>516</v>
+      </c>
+      <c r="E113" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>417</v>
-      </c>
-      <c r="C114" t="s">
-        <v>163</v>
-      </c>
-      <c r="D114" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>427</v>
+      </c>
+      <c r="C114" s="30" t="s">
+        <v>469</v>
+      </c>
+      <c r="D114" s="26" t="s">
+        <v>517</v>
+      </c>
+      <c r="E114" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>417</v>
-      </c>
-      <c r="C115" t="s">
-        <v>165</v>
-      </c>
-      <c r="D115" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B115" s="27" t="s">
+        <v>428</v>
+      </c>
+      <c r="C115" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="D115" s="26" t="s">
+        <v>518</v>
+      </c>
+      <c r="E115" s="30" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>417</v>
-      </c>
-      <c r="C116" t="s">
-        <v>166</v>
-      </c>
-      <c r="D116" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B116" s="27" t="s">
+        <v>429</v>
+      </c>
+      <c r="C116" s="30" t="s">
+        <v>471</v>
+      </c>
+      <c r="D116" s="26" t="s">
+        <v>519</v>
+      </c>
+      <c r="E116" s="30" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>417</v>
-      </c>
-      <c r="C117" t="s">
-        <v>167</v>
-      </c>
-      <c r="D117" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C117" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="D117" s="26" t="s">
+        <v>520</v>
+      </c>
+      <c r="E117" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>417</v>
-      </c>
-      <c r="C118" t="s">
-        <v>169</v>
-      </c>
-      <c r="D118" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C118" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="D118" s="26" t="s">
+        <v>521</v>
+      </c>
+      <c r="E118" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>417</v>
-      </c>
-      <c r="C119" t="s">
-        <v>170</v>
-      </c>
-      <c r="D119" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B119" s="26" t="s">
+        <v>430</v>
+      </c>
+      <c r="C119" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="D119" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="E119" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>417</v>
-      </c>
-      <c r="C120" t="s">
-        <v>171</v>
-      </c>
-      <c r="D120" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>431</v>
+      </c>
+      <c r="C120" s="30" t="s">
+        <v>472</v>
+      </c>
+      <c r="D120" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="E120" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>417</v>
-      </c>
-      <c r="C121" t="s">
-        <v>172</v>
-      </c>
-      <c r="D121" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B121" s="26" t="s">
+        <v>431</v>
+      </c>
+      <c r="C121" s="31" t="s">
+        <v>473</v>
+      </c>
+      <c r="D121" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="E121" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>417</v>
-      </c>
-      <c r="C122" t="s">
-        <v>173</v>
-      </c>
-      <c r="D122" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>431</v>
+      </c>
+      <c r="C122" s="30" t="s">
+        <v>474</v>
+      </c>
+      <c r="D122" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="E122" s="30" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>417</v>
-      </c>
-      <c r="C123" t="s">
-        <v>175</v>
-      </c>
-      <c r="D123" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>432</v>
+      </c>
+      <c r="C123" s="31" t="s">
+        <v>475</v>
+      </c>
+      <c r="D123" s="26" t="s">
+        <v>526</v>
+      </c>
+      <c r="E123" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" ht="27" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>417</v>
-      </c>
-      <c r="C124" t="s">
-        <v>177</v>
-      </c>
-      <c r="D124" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>433</v>
+      </c>
+      <c r="C124" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="D124" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="E124" s="30" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>417</v>
-      </c>
-      <c r="C125" t="s">
-        <v>179</v>
-      </c>
-      <c r="D125" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B125" s="26" t="s">
+        <v>434</v>
+      </c>
+      <c r="C125" s="30" t="s">
+        <v>459</v>
+      </c>
+      <c r="D125" s="26" t="s">
+        <v>528</v>
+      </c>
+      <c r="E125" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" ht="18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>181</v>
-      </c>
-      <c r="C126" t="s">
-        <v>182</v>
-      </c>
-      <c r="D126" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="C126" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="D126" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="E126" s="30" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>181</v>
-      </c>
-      <c r="C127" t="s">
-        <v>183</v>
-      </c>
-      <c r="D127" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B127" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="C127" s="33" t="s">
+        <v>535</v>
+      </c>
+      <c r="D127" s="32" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="36" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>181</v>
-      </c>
-      <c r="C128" t="s">
-        <v>184</v>
-      </c>
-      <c r="D128" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B128" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C128" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="D128" s="32" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>181</v>
-      </c>
-      <c r="C129" t="s">
-        <v>8</v>
-      </c>
-      <c r="D129" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B129" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>453</v>
+      </c>
+      <c r="D129" s="32" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>181</v>
-      </c>
-      <c r="C130" t="s">
-        <v>186</v>
-      </c>
-      <c r="D130" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="C130" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="D130" s="32" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>181</v>
-      </c>
-      <c r="C131" t="s">
-        <v>187</v>
-      </c>
-      <c r="D131" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="C131" s="31" t="s">
+        <v>536</v>
+      </c>
+      <c r="D131" s="32" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="36" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>181</v>
-      </c>
-      <c r="C132" t="s">
-        <v>189</v>
-      </c>
-      <c r="D132" t="s">
-        <v>190</v>
+        <v>301</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C132" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="D132" s="32" t="s">
+        <v>539</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>181</v>
-      </c>
-      <c r="C133" t="s">
-        <v>191</v>
-      </c>
-      <c r="D133" t="s">
-        <v>83</v>
+        <v>301</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="C133" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="D133" s="26" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>181</v>
-      </c>
-      <c r="C134" t="s">
-        <v>192</v>
-      </c>
-      <c r="D134" t="s">
-        <v>83</v>
+        <v>301</v>
+      </c>
+      <c r="B134" s="32" t="s">
+        <v>540</v>
+      </c>
+      <c r="C134" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="D134" s="32" t="s">
+        <v>547</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>181</v>
-      </c>
-      <c r="C135" t="s">
-        <v>193</v>
-      </c>
-      <c r="D135" t="s">
-        <v>83</v>
+        <v>301</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>426</v>
+      </c>
+      <c r="C135" s="30" t="s">
+        <v>465</v>
+      </c>
+      <c r="D135" s="26" t="s">
+        <v>548</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>181</v>
-      </c>
-      <c r="C136" t="s">
-        <v>194</v>
-      </c>
-      <c r="D136" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B136" s="32" t="s">
+        <v>427</v>
+      </c>
+      <c r="C136" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="D136" s="32" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>181</v>
-      </c>
-      <c r="C137" t="s">
-        <v>195</v>
-      </c>
-      <c r="D137" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="B137" s="26" t="s">
+        <v>541</v>
+      </c>
+      <c r="C137" s="30" t="s">
+        <v>546</v>
+      </c>
+      <c r="D137" s="26" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>181</v>
-      </c>
-      <c r="C138" t="s">
-        <v>10</v>
-      </c>
-      <c r="D138" t="s">
-        <v>11</v>
+        <v>301</v>
+      </c>
+      <c r="B138" s="32" t="s">
+        <v>542</v>
+      </c>
+      <c r="C138" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="D138" s="32" t="s">
+        <v>551</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>181</v>
-      </c>
-      <c r="C139" t="s">
-        <v>196</v>
-      </c>
-      <c r="D139" t="s">
-        <v>12</v>
+        <v>301</v>
+      </c>
+      <c r="B139" s="32" t="s">
+        <v>543</v>
+      </c>
+      <c r="C139" s="33" t="s">
+        <v>544</v>
+      </c>
+      <c r="D139" s="32" t="s">
+        <v>552</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>181</v>
-      </c>
-      <c r="C140" t="s">
-        <v>197</v>
-      </c>
-      <c r="D140" t="s">
-        <v>89</v>
+        <v>301</v>
+      </c>
+      <c r="B140" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="C140" s="30" t="s">
+        <v>477</v>
+      </c>
+      <c r="D140" s="26" t="s">
+        <v>553</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C141" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="D141" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C142" t="s">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="D142" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C143" t="s">
-        <v>200</v>
+        <v>93</v>
       </c>
       <c r="D143" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C144" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D144" t="s">
-        <v>95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C145" t="s">
-        <v>201</v>
+        <v>94</v>
       </c>
       <c r="D145" t="s">
-        <v>202</v>
+        <v>95</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C146" t="s">
-        <v>203</v>
+        <v>96</v>
       </c>
       <c r="D146" t="s">
-        <v>98</v>
+        <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C147" t="s">
-        <v>204</v>
+        <v>97</v>
       </c>
       <c r="D147" t="s">
-        <v>205</v>
+        <v>98</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C148" t="s">
-        <v>206</v>
+        <v>99</v>
       </c>
       <c r="D148" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C149" t="s">
-        <v>207</v>
+        <v>100</v>
       </c>
       <c r="D149" t="s">
-        <v>208</v>
+        <v>101</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C150" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="D150" t="s">
-        <v>210</v>
+        <v>103</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C151" t="s">
-        <v>211</v>
+        <v>104</v>
       </c>
       <c r="D151" t="s">
-        <v>210</v>
+        <v>103</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C152" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D152" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C153" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D153" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C154" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="D154" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C155" t="s">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="D155" t="s">
-        <v>215</v>
+        <v>108</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C156" t="s">
-        <v>216</v>
+        <v>109</v>
       </c>
       <c r="D156" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C157" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D157" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C158" t="s">
-        <v>217</v>
+        <v>110</v>
       </c>
       <c r="D158" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C159" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D159" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C160" t="s">
-        <v>218</v>
+        <v>111</v>
       </c>
       <c r="D160" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C161" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D161" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C162" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D162" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C163" t="s">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="D163" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C164" t="s">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="D164" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C165" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="D165" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="D166" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C167" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D167" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C168" t="s">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="D168" t="s">
-        <v>225</v>
+        <v>118</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C169" t="s">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="D169" t="s">
-        <v>225</v>
+        <v>118</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C170" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="D170" t="s">
-        <v>225</v>
+        <v>118</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C171" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="D171" t="s">
-        <v>226</v>
+        <v>119</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C172" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D172" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C173" t="s">
-        <v>219</v>
+        <v>112</v>
       </c>
       <c r="D173" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C174" t="s">
-        <v>221</v>
+        <v>114</v>
       </c>
       <c r="D174" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C175" t="s">
-        <v>227</v>
+        <v>120</v>
       </c>
       <c r="D175" t="s">
-        <v>220</v>
+        <v>113</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C176" t="s">
-        <v>223</v>
+        <v>116</v>
       </c>
       <c r="D176" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C177" t="s">
-        <v>228</v>
+        <v>121</v>
       </c>
       <c r="D177" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C178" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C179" t="s">
-        <v>229</v>
+        <v>122</v>
       </c>
       <c r="D179" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C180" t="s">
-        <v>231</v>
+        <v>124</v>
       </c>
       <c r="D180" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C181" t="s">
-        <v>232</v>
+        <v>125</v>
       </c>
       <c r="D181" t="s">
-        <v>230</v>
+        <v>123</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C182" t="s">
-        <v>233</v>
+        <v>126</v>
       </c>
       <c r="D182" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C183" t="s">
-        <v>235</v>
+        <v>128</v>
       </c>
       <c r="D183" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C184" t="s">
-        <v>236</v>
+        <v>129</v>
       </c>
       <c r="D184" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C185" t="s">
-        <v>237</v>
+        <v>130</v>
       </c>
       <c r="D185" t="s">
-        <v>238</v>
+        <v>131</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C186" t="s">
-        <v>239</v>
+        <v>132</v>
       </c>
       <c r="D186" t="s">
-        <v>240</v>
+        <v>133</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C187" t="s">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="D187" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C188" t="s">
-        <v>242</v>
+        <v>135</v>
       </c>
       <c r="D188" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C189" t="s">
-        <v>243</v>
+        <v>136</v>
       </c>
       <c r="D189" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C190" t="s">
-        <v>244</v>
+        <v>137</v>
       </c>
       <c r="D190" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C191" t="s">
-        <v>245</v>
+        <v>138</v>
       </c>
       <c r="D191" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C192" t="s">
-        <v>246</v>
+        <v>139</v>
       </c>
       <c r="D192" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C193" t="s">
-        <v>247</v>
+        <v>140</v>
       </c>
       <c r="D193" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C194" t="s">
-        <v>248</v>
+        <v>141</v>
       </c>
       <c r="D194" t="s">
-        <v>126</v>
+        <v>74</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C195" t="s">
-        <v>249</v>
+        <v>142</v>
       </c>
       <c r="D195" t="s">
-        <v>250</v>
+        <v>143</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C196" t="s">
-        <v>251</v>
+        <v>144</v>
       </c>
       <c r="D196" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C197" t="s">
-        <v>252</v>
+        <v>145</v>
       </c>
       <c r="D197" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C198" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D198" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C199" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D199" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C200" t="s">
-        <v>253</v>
+        <v>146</v>
       </c>
       <c r="D200" t="s">
-        <v>138</v>
+        <v>78</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C201" t="s">
-        <v>254</v>
+        <v>147</v>
       </c>
       <c r="D201" t="s">
-        <v>140</v>
+        <v>79</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C202" t="s">
-        <v>255</v>
+        <v>148</v>
       </c>
       <c r="D202" t="s">
-        <v>256</v>
+        <v>149</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C203" t="s">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="D203" t="s">
-        <v>256</v>
+        <v>149</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C204" t="s">
-        <v>258</v>
+        <v>151</v>
       </c>
       <c r="D204" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C205" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="D205" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>152</v>
       </c>
       <c r="D206" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C207" t="s">
-        <v>260</v>
+        <v>153</v>
       </c>
       <c r="D207" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C208" t="s">
-        <v>262</v>
+        <v>155</v>
       </c>
       <c r="D208" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>156</v>
       </c>
       <c r="D209" t="s">
-        <v>149</v>
+        <v>81</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C210" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D210" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C211" t="s">
-        <v>264</v>
+        <v>157</v>
       </c>
       <c r="D211" t="s">
-        <v>265</v>
+        <v>158</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C212" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D212" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C213" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D213" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C214" t="s">
-        <v>266</v>
+        <v>159</v>
       </c>
       <c r="D214" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C215" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D215" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C216" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="D216" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C217" t="s">
-        <v>267</v>
+        <v>160</v>
       </c>
       <c r="D217" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C218" t="s">
-        <v>268</v>
+        <v>161</v>
       </c>
       <c r="D218" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C219" t="s">
-        <v>269</v>
+        <v>162</v>
       </c>
       <c r="D219" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C220" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="D220" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C221" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D221" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C222" t="s">
-        <v>270</v>
+        <v>163</v>
       </c>
       <c r="D222" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C223" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D223" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C224" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
       <c r="D224" t="s">
-        <v>162</v>
+        <v>84</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C225" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="D225" t="s">
-        <v>272</v>
+        <v>165</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C226" t="s">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="D226" t="s">
-        <v>274</v>
+        <v>167</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C227" t="s">
-        <v>275</v>
+        <v>168</v>
       </c>
       <c r="D227" t="s">
-        <v>164</v>
+        <v>85</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C228" t="s">
-        <v>276</v>
+        <v>169</v>
       </c>
       <c r="D228" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C229" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D229" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C230" t="s">
-        <v>277</v>
+        <v>170</v>
       </c>
       <c r="D230" t="s">
-        <v>278</v>
+        <v>171</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C231" t="s">
-        <v>279</v>
+        <v>172</v>
       </c>
       <c r="D231" t="s">
-        <v>280</v>
+        <v>173</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C232" t="s">
-        <v>167</v>
+        <v>86</v>
       </c>
       <c r="D232" t="s">
-        <v>168</v>
+        <v>87</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C233" t="s">
-        <v>281</v>
+        <v>174</v>
       </c>
       <c r="D233" t="s">
-        <v>256</v>
+        <v>149</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C234" t="s">
-        <v>282</v>
+        <v>175</v>
       </c>
       <c r="D234" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C235" t="s">
-        <v>283</v>
+        <v>176</v>
       </c>
       <c r="D235" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C236" t="s">
-        <v>284</v>
+        <v>177</v>
       </c>
       <c r="D236" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C237" t="s">
-        <v>285</v>
+        <v>178</v>
       </c>
       <c r="D237" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C238" t="s">
-        <v>286</v>
+        <v>179</v>
       </c>
       <c r="D238" t="s">
-        <v>278</v>
+        <v>171</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C239" t="s">
-        <v>287</v>
+        <v>180</v>
       </c>
       <c r="D239" t="s">
-        <v>280</v>
+        <v>173</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>343</v>
+      </c>
+      <c r="C240" t="s">
         <v>181</v>
       </c>
-      <c r="C240" t="s">
-        <v>288</v>
-      </c>
       <c r="D240" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C241" t="s">
-        <v>289</v>
+        <v>182</v>
       </c>
       <c r="D241" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C242" t="s">
-        <v>290</v>
+        <v>183</v>
       </c>
       <c r="D242" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>181</v>
+        <v>343</v>
       </c>
       <c r="C243" t="s">
-        <v>291</v>
+        <v>184</v>
       </c>
       <c r="D243" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
-        <v>292</v>
-      </c>
-      <c r="C244" t="s">
-        <v>293</v>
-      </c>
-      <c r="D244" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
-        <v>292</v>
-      </c>
-      <c r="C245" t="s">
-        <v>13</v>
-      </c>
-      <c r="D245" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
-        <v>292</v>
-      </c>
-      <c r="C246" t="s">
-        <v>294</v>
-      </c>
-      <c r="D246" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
-        <v>292</v>
-      </c>
-      <c r="C247" t="s">
-        <v>295</v>
-      </c>
-      <c r="D247" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
-        <v>292</v>
-      </c>
-      <c r="C248" t="s">
-        <v>19</v>
-      </c>
-      <c r="D248" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
-        <v>292</v>
-      </c>
-      <c r="C249" t="s">
-        <v>296</v>
-      </c>
-      <c r="D249" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>292</v>
-      </c>
-      <c r="C250" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A244" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B244" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C244" s="20" t="s">
+        <v>314</v>
+      </c>
+      <c r="D244" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="E244" s="21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A245" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B245" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C245" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="D245" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="E245" s="22" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A246" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B246" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="C246" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="D246" s="20" t="s">
+        <v>327</v>
+      </c>
+      <c r="E246" s="21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A247" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B247" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="C247" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="D247" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="E247" s="21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A248" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B248" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C248" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="D248" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="E248" s="22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A249" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B249" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C249" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="D249" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="E249" s="22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A250" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B250" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C250" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="D250" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E250" s="22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A251" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B251" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C251" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="D251" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E251" s="22" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A252" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B252" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="C252" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="D252" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="E252" s="21" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A253" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B253" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C253" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="D253" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="E253" s="22" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A254" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B254" s="20" t="s">
+        <v>309</v>
+      </c>
+      <c r="C254" s="20" t="s">
+        <v>321</v>
+      </c>
+      <c r="D254" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="E254" s="22" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A255" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B255" s="20" t="s">
+        <v>310</v>
+      </c>
+      <c r="C255" s="20" t="s">
+        <v>322</v>
+      </c>
+      <c r="D255" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="E255" s="22" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A256" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B256" s="20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C256" s="20" t="s">
+        <v>323</v>
+      </c>
+      <c r="D256" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="E256" s="22" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="27" x14ac:dyDescent="0.25">
+      <c r="A257" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B257" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C257" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="D257" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="E257" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B258" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="C258" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="D258" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D250" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
-        <v>292</v>
-      </c>
-      <c r="C251" t="s">
-        <v>297</v>
-      </c>
-      <c r="D251" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
-        <v>292</v>
-      </c>
-      <c r="C252" t="s">
-        <v>31</v>
-      </c>
-      <c r="D252" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
-        <v>292</v>
-      </c>
-      <c r="C253" t="s">
-        <v>33</v>
-      </c>
-      <c r="D253" t="s">
+      <c r="E258" s="18"/>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B259" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C259" t="s">
+        <v>241</v>
+      </c>
+      <c r="D259" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>292</v>
-      </c>
-      <c r="C254" t="s">
-        <v>35</v>
-      </c>
-      <c r="D254" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>292</v>
-      </c>
-      <c r="C255" t="s">
-        <v>46</v>
-      </c>
-      <c r="D255" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>292</v>
-      </c>
-      <c r="C256" t="s">
-        <v>299</v>
-      </c>
-      <c r="D256" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A257" t="s">
-        <v>292</v>
-      </c>
-      <c r="C257" t="s">
-        <v>300</v>
-      </c>
-      <c r="D257" t="s">
-        <v>65</v>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B260" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C260" t="s">
+        <v>345</v>
+      </c>
+      <c r="D260" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/database_manutenzione.xlsx
+++ b/database_manutenzione.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="343">
   <si>
     <t>Scadenza</t>
   </si>
@@ -1180,336 +1180,6 @@
   </si>
   <si>
     <t>https://app.box.com/s/3ujx7hztq0aupkrfqrdn71lgnkvm21xq</t>
-  </si>
-  <si>
-    <t>F4</t>
-  </si>
-  <si>
-    <t>F5</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>F13</t>
-  </si>
-  <si>
-    <t>F14</t>
-  </si>
-  <si>
-    <t>F15</t>
-  </si>
-  <si>
-    <t>F16</t>
-  </si>
-  <si>
-    <t>F17</t>
-  </si>
-  <si>
-    <t>F18</t>
-  </si>
-  <si>
-    <t>F19</t>
-  </si>
-  <si>
-    <t>F20</t>
-  </si>
-  <si>
-    <t>F21</t>
-  </si>
-  <si>
-    <t>F22</t>
-  </si>
-  <si>
-    <t>F23</t>
-  </si>
-  <si>
-    <t>F24</t>
-  </si>
-  <si>
-    <t>F25</t>
-  </si>
-  <si>
-    <t>F26</t>
-  </si>
-  <si>
-    <t>F27</t>
-  </si>
-  <si>
-    <t>F28</t>
-  </si>
-  <si>
-    <t>F29</t>
-  </si>
-  <si>
-    <t>F30</t>
-  </si>
-  <si>
-    <t>F31</t>
-  </si>
-  <si>
-    <t>F32</t>
-  </si>
-  <si>
-    <t>F33</t>
-  </si>
-  <si>
-    <t>F34</t>
-  </si>
-  <si>
-    <t>F35</t>
-  </si>
-  <si>
-    <t>F36</t>
-  </si>
-  <si>
-    <t>F37</t>
-  </si>
-  <si>
-    <t>F38</t>
-  </si>
-  <si>
-    <t>F39</t>
-  </si>
-  <si>
-    <t>F40</t>
-  </si>
-  <si>
-    <t>F41</t>
-  </si>
-  <si>
-    <t>F42</t>
-  </si>
-  <si>
-    <t>F43</t>
-  </si>
-  <si>
-    <t>F44</t>
-  </si>
-  <si>
-    <t>F45</t>
-  </si>
-  <si>
-    <t>F46</t>
-  </si>
-  <si>
-    <t>F47</t>
-  </si>
-  <si>
-    <t>F48</t>
-  </si>
-  <si>
-    <t>F49</t>
-  </si>
-  <si>
-    <t>F50</t>
-  </si>
-  <si>
-    <t>F51</t>
-  </si>
-  <si>
-    <t>F52</t>
-  </si>
-  <si>
-    <t>F53</t>
-  </si>
-  <si>
-    <t>F54</t>
-  </si>
-  <si>
-    <t>F55</t>
-  </si>
-  <si>
-    <t>F56</t>
-  </si>
-  <si>
-    <t>F57</t>
-  </si>
-  <si>
-    <t>F58</t>
-  </si>
-  <si>
-    <t>F59</t>
-  </si>
-  <si>
-    <t>F60</t>
-  </si>
-  <si>
-    <t>F61</t>
-  </si>
-  <si>
-    <t>F62</t>
-  </si>
-  <si>
-    <t>F63</t>
-  </si>
-  <si>
-    <t>F64</t>
-  </si>
-  <si>
-    <t>F65</t>
-  </si>
-  <si>
-    <t>F66</t>
-  </si>
-  <si>
-    <t>F67</t>
-  </si>
-  <si>
-    <t>F68</t>
-  </si>
-  <si>
-    <t>F69</t>
-  </si>
-  <si>
-    <t>F70</t>
-  </si>
-  <si>
-    <t>F71</t>
-  </si>
-  <si>
-    <t>F72</t>
-  </si>
-  <si>
-    <t>F73</t>
-  </si>
-  <si>
-    <t>F74</t>
-  </si>
-  <si>
-    <t>F75</t>
-  </si>
-  <si>
-    <t>F76</t>
-  </si>
-  <si>
-    <t>F77</t>
-  </si>
-  <si>
-    <t>F78</t>
-  </si>
-  <si>
-    <t>F79</t>
-  </si>
-  <si>
-    <t>F80</t>
-  </si>
-  <si>
-    <t>F81</t>
-  </si>
-  <si>
-    <t>F82</t>
-  </si>
-  <si>
-    <t>F83</t>
-  </si>
-  <si>
-    <t>F84</t>
-  </si>
-  <si>
-    <t>F85</t>
-  </si>
-  <si>
-    <t>F86</t>
-  </si>
-  <si>
-    <t>F87</t>
-  </si>
-  <si>
-    <t>F88</t>
-  </si>
-  <si>
-    <t>F89</t>
-  </si>
-  <si>
-    <t>F90</t>
-  </si>
-  <si>
-    <t>F91</t>
-  </si>
-  <si>
-    <t>F92</t>
-  </si>
-  <si>
-    <t>F93</t>
-  </si>
-  <si>
-    <t>F94</t>
-  </si>
-  <si>
-    <t>F95</t>
-  </si>
-  <si>
-    <t>F96</t>
-  </si>
-  <si>
-    <t>F97</t>
-  </si>
-  <si>
-    <t>F98</t>
-  </si>
-  <si>
-    <t>F99</t>
-  </si>
-  <si>
-    <t>F100</t>
-  </si>
-  <si>
-    <t>F101</t>
-  </si>
-  <si>
-    <t>F102</t>
-  </si>
-  <si>
-    <t>F103</t>
-  </si>
-  <si>
-    <t>F104</t>
-  </si>
-  <si>
-    <t>F105</t>
-  </si>
-  <si>
-    <t>F106</t>
-  </si>
-  <si>
-    <t>F107</t>
-  </si>
-  <si>
-    <t>F108</t>
-  </si>
-  <si>
-    <t>F109</t>
-  </si>
-  <si>
-    <t>F110</t>
-  </si>
-  <si>
-    <t>F111</t>
-  </si>
-  <si>
-    <t>F112</t>
-  </si>
-  <si>
-    <t>F113</t>
   </si>
   <si>
     <t>https://app.box.com/s/ynsd6x9i2a4cx4gh8z5qf70fyucygoeg|https://app.box.com/s/d7vvy4eq3ia4aekn8w3g78b15uukrbog</t>
@@ -2162,7 +1832,7 @@
     </row>
     <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>340</v>
+        <v>122</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>5</v>
@@ -2182,7 +1852,7 @@
     </row>
     <row r="4" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>341</v>
+        <v>122</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>123</v>
@@ -2202,7 +1872,7 @@
     </row>
     <row r="5" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>342</v>
+        <v>122</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>115</v>
@@ -2222,7 +1892,7 @@
     </row>
     <row r="6" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>343</v>
+        <v>122</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>116</v>
@@ -2242,7 +1912,7 @@
     </row>
     <row r="7" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>177</v>
@@ -2262,7 +1932,7 @@
     </row>
     <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>345</v>
+        <v>122</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>181</v>
@@ -2282,7 +1952,7 @@
     </row>
     <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>346</v>
+        <v>122</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>125</v>
@@ -2302,7 +1972,7 @@
     </row>
     <row r="10" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>347</v>
+        <v>122</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>126</v>
@@ -2322,7 +1992,7 @@
     </row>
     <row r="11" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>348</v>
+        <v>122</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>187</v>
@@ -2342,7 +2012,7 @@
     </row>
     <row r="12" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>349</v>
+        <v>122</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>128</v>
@@ -2362,7 +2032,7 @@
     </row>
     <row r="13" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>350</v>
+        <v>122</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>129</v>
@@ -2382,7 +2052,7 @@
     </row>
     <row r="14" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>351</v>
+        <v>122</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>117</v>
@@ -2402,7 +2072,7 @@
     </row>
     <row r="15" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>352</v>
+        <v>122</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>64</v>
@@ -2422,7 +2092,7 @@
     </row>
     <row r="16" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>353</v>
+        <v>122</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>64</v>
@@ -2442,7 +2112,7 @@
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>354</v>
+        <v>122</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>132</v>
@@ -2462,7 +2132,7 @@
     </row>
     <row r="18" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>355</v>
+        <v>122</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>134</v>
@@ -2482,7 +2152,7 @@
     </row>
     <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>356</v>
+        <v>122</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>136</v>
@@ -2502,7 +2172,7 @@
     </row>
     <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>357</v>
+        <v>122</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>138</v>
@@ -2522,7 +2192,7 @@
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>358</v>
+        <v>122</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>198</v>
@@ -2542,7 +2212,7 @@
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>359</v>
+        <v>122</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>142</v>
@@ -2562,7 +2232,7 @@
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>360</v>
+        <v>122</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>144</v>
@@ -2582,7 +2252,7 @@
     </row>
     <row r="24" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>361</v>
+        <v>122</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>203</v>
@@ -2602,7 +2272,7 @@
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>362</v>
+        <v>122</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>67</v>
@@ -2622,7 +2292,7 @@
     </row>
     <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>363</v>
+        <v>122</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>209</v>
@@ -2642,7 +2312,7 @@
     </row>
     <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>364</v>
+        <v>122</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>213</v>
@@ -2662,7 +2332,7 @@
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>365</v>
+        <v>122</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>217</v>
@@ -2682,7 +2352,7 @@
     </row>
     <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>366</v>
+        <v>122</v>
       </c>
       <c r="B29" s="20" t="s">
         <v>219</v>
@@ -2702,7 +2372,7 @@
     </row>
     <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>367</v>
+        <v>122</v>
       </c>
       <c r="B30" s="20" t="s">
         <v>222</v>
@@ -2722,7 +2392,7 @@
     </row>
     <row r="31" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>368</v>
+        <v>122</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>225</v>
@@ -2742,7 +2412,7 @@
     </row>
     <row r="32" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>369</v>
+        <v>122</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>229</v>
@@ -2762,7 +2432,7 @@
     </row>
     <row r="33" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>370</v>
+        <v>122</v>
       </c>
       <c r="B33" s="12" t="s">
         <v>69</v>
@@ -2782,7 +2452,7 @@
     </row>
     <row r="34" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>371</v>
+        <v>122</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>69</v>
@@ -2802,7 +2472,7 @@
     </row>
     <row r="35" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>372</v>
+        <v>122</v>
       </c>
       <c r="B35" s="22" t="s">
         <v>74</v>
@@ -2822,7 +2492,7 @@
     </row>
     <row r="36" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>373</v>
+        <v>122</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>74</v>
@@ -2842,7 +2512,7 @@
     </row>
     <row r="37" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>374</v>
+        <v>122</v>
       </c>
       <c r="B37" s="12" t="s">
         <v>145</v>
@@ -2862,7 +2532,7 @@
     </row>
     <row r="38" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>375</v>
+        <v>122</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>237</v>
@@ -2882,7 +2552,7 @@
     </row>
     <row r="39" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>376</v>
+        <v>122</v>
       </c>
       <c r="B39" s="20" t="s">
         <v>239</v>
@@ -2902,7 +2572,7 @@
     </row>
     <row r="40" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>377</v>
+        <v>122</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>242</v>
@@ -2922,7 +2592,7 @@
     </row>
     <row r="41" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>378</v>
+        <v>122</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>244</v>
@@ -2942,7 +2612,7 @@
     </row>
     <row r="42" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>379</v>
+        <v>122</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>245</v>
@@ -2962,7 +2632,7 @@
     </row>
     <row r="43" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>380</v>
+        <v>122</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>247</v>
@@ -2982,7 +2652,7 @@
     </row>
     <row r="44" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>381</v>
+        <v>122</v>
       </c>
       <c r="B44" s="20" t="s">
         <v>239</v>
@@ -3002,7 +2672,7 @@
     </row>
     <row r="45" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>382</v>
+        <v>122</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>242</v>
@@ -3022,7 +2692,7 @@
     </row>
     <row r="46" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>383</v>
+        <v>122</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>244</v>
@@ -3042,7 +2712,7 @@
     </row>
     <row r="47" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>384</v>
+        <v>122</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>245</v>
@@ -3062,7 +2732,7 @@
     </row>
     <row r="48" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>385</v>
+        <v>122</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>247</v>
@@ -3082,7 +2752,7 @@
     </row>
     <row r="49" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>386</v>
+        <v>122</v>
       </c>
       <c r="B49" s="20" t="s">
         <v>239</v>
@@ -3102,7 +2772,7 @@
     </row>
     <row r="50" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>387</v>
+        <v>122</v>
       </c>
       <c r="B50" s="12" t="s">
         <v>242</v>
@@ -3122,7 +2792,7 @@
     </row>
     <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>388</v>
+        <v>122</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>244</v>
@@ -3142,7 +2812,7 @@
     </row>
     <row r="52" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>389</v>
+        <v>122</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>245</v>
@@ -3162,7 +2832,7 @@
     </row>
     <row r="53" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>390</v>
+        <v>122</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>247</v>
@@ -3182,7 +2852,7 @@
     </row>
     <row r="54" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>391</v>
+        <v>122</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>75</v>
@@ -3202,7 +2872,7 @@
     </row>
     <row r="55" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>392</v>
+        <v>122</v>
       </c>
       <c r="B55" s="22" t="s">
         <v>76</v>
@@ -3222,7 +2892,7 @@
     </row>
     <row r="56" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>393</v>
+        <v>122</v>
       </c>
       <c r="B56" s="17" t="s">
         <v>256</v>
@@ -3242,7 +2912,7 @@
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>394</v>
+        <v>122</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>259</v>
@@ -3262,7 +2932,7 @@
     </row>
     <row r="58" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>395</v>
+        <v>122</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>262</v>
@@ -3282,7 +2952,7 @@
     </row>
     <row r="59" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>396</v>
+        <v>122</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>263</v>
@@ -3302,7 +2972,7 @@
     </row>
     <row r="60" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>397</v>
+        <v>122</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>266</v>
@@ -3322,7 +2992,7 @@
     </row>
     <row r="61" spans="1:6" ht="57" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>398</v>
+        <v>122</v>
       </c>
       <c r="B61" s="12" t="s">
         <v>77</v>
@@ -3342,7 +3012,7 @@
     </row>
     <row r="62" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>399</v>
+        <v>122</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>269</v>
@@ -3362,7 +3032,7 @@
     </row>
     <row r="63" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>400</v>
+        <v>122</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>272</v>
@@ -3382,7 +3052,7 @@
     </row>
     <row r="64" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>401</v>
+        <v>122</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>274</v>
@@ -3402,7 +3072,7 @@
     </row>
     <row r="65" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>402</v>
+        <v>122</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>93</v>
@@ -3417,12 +3087,12 @@
         <v>121</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>451</v>
+        <v>341</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>403</v>
+        <v>122</v>
       </c>
       <c r="B66" s="12" t="s">
         <v>78</v>
@@ -3442,7 +3112,7 @@
     </row>
     <row r="67" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>404</v>
+        <v>122</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>78</v>
@@ -3462,7 +3132,7 @@
     </row>
     <row r="68" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>405</v>
+        <v>122</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>79</v>
@@ -3482,7 +3152,7 @@
     </row>
     <row r="69" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>406</v>
+        <v>122</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>79</v>
@@ -3502,7 +3172,7 @@
     </row>
     <row r="70" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>407</v>
+        <v>122</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>80</v>
@@ -3522,7 +3192,7 @@
     </row>
     <row r="71" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>408</v>
+        <v>122</v>
       </c>
       <c r="B71" s="12" t="s">
         <v>80</v>
@@ -3542,7 +3212,7 @@
     </row>
     <row r="72" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>409</v>
+        <v>122</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>80</v>
@@ -3562,7 +3232,7 @@
     </row>
     <row r="73" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>410</v>
+        <v>122</v>
       </c>
       <c r="B73" s="22" t="s">
         <v>80</v>
@@ -3582,7 +3252,7 @@
     </row>
     <row r="74" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>411</v>
+        <v>122</v>
       </c>
       <c r="B74" s="17" t="s">
         <v>80</v>
@@ -3602,7 +3272,7 @@
     </row>
     <row r="75" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>412</v>
+        <v>122</v>
       </c>
       <c r="B75" s="12" t="s">
         <v>81</v>
@@ -3622,7 +3292,7 @@
     </row>
     <row r="76" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>413</v>
+        <v>122</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>81</v>
@@ -3637,12 +3307,12 @@
         <v>119</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>452</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>414</v>
+        <v>122</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>82</v>
@@ -3657,12 +3327,12 @@
         <v>120</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>450</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>415</v>
+        <v>122</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>82</v>
@@ -3682,7 +3352,7 @@
     </row>
     <row r="79" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>416</v>
+        <v>122</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>82</v>
@@ -3702,7 +3372,7 @@
     </row>
     <row r="80" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>417</v>
+        <v>122</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>82</v>
@@ -3722,7 +3392,7 @@
     </row>
     <row r="81" spans="1:6" ht="114" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>418</v>
+        <v>122</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>82</v>
@@ -3742,7 +3412,7 @@
     </row>
     <row r="82" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>419</v>
+        <v>122</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>82</v>
@@ -3762,7 +3432,7 @@
     </row>
     <row r="83" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>420</v>
+        <v>122</v>
       </c>
       <c r="B83" s="12" t="s">
         <v>155</v>
@@ -3782,7 +3452,7 @@
     </row>
     <row r="84" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>421</v>
+        <v>122</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>83</v>
@@ -3802,7 +3472,7 @@
     </row>
     <row r="85" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>422</v>
+        <v>122</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>84</v>
@@ -3822,7 +3492,7 @@
     </row>
     <row r="86" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>423</v>
+        <v>122</v>
       </c>
       <c r="B86" s="12" t="s">
         <v>157</v>
@@ -3842,7 +3512,7 @@
     </row>
     <row r="87" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>424</v>
+        <v>122</v>
       </c>
       <c r="B87" s="12" t="s">
         <v>164</v>
@@ -3862,7 +3532,7 @@
     </row>
     <row r="88" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>425</v>
+        <v>122</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>158</v>
@@ -3882,7 +3552,7 @@
     </row>
     <row r="89" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>426</v>
+        <v>122</v>
       </c>
       <c r="B89" s="12" t="s">
         <v>85</v>
@@ -3902,7 +3572,7 @@
     </row>
     <row r="90" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>427</v>
+        <v>122</v>
       </c>
       <c r="B90" s="12" t="s">
         <v>159</v>
@@ -3922,7 +3592,7 @@
     </row>
     <row r="91" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>428</v>
+        <v>122</v>
       </c>
       <c r="B91" s="12" t="s">
         <v>86</v>
@@ -3942,7 +3612,7 @@
     </row>
     <row r="92" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>429</v>
+        <v>122</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>87</v>
@@ -3962,7 +3632,7 @@
     </row>
     <row r="93" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>430</v>
+        <v>122</v>
       </c>
       <c r="B93" s="12" t="s">
         <v>87</v>
@@ -3982,7 +3652,7 @@
     </row>
     <row r="94" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>431</v>
+        <v>122</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>87</v>
@@ -4002,7 +3672,7 @@
     </row>
     <row r="95" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>432</v>
+        <v>122</v>
       </c>
       <c r="B95" s="17" t="s">
         <v>88</v>
@@ -4022,7 +3692,7 @@
     </row>
     <row r="96" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>433</v>
+        <v>122</v>
       </c>
       <c r="B96" s="12" t="s">
         <v>88</v>
@@ -4042,7 +3712,7 @@
     </row>
     <row r="97" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>434</v>
+        <v>122</v>
       </c>
       <c r="B97" s="12" t="s">
         <v>312</v>
@@ -4062,7 +3732,7 @@
     </row>
     <row r="98" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>435</v>
+        <v>122</v>
       </c>
       <c r="B98" s="20" t="s">
         <v>313</v>
@@ -4082,7 +3752,7 @@
     </row>
     <row r="99" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>436</v>
+        <v>122</v>
       </c>
       <c r="B99" s="12" t="s">
         <v>89</v>
@@ -4102,7 +3772,7 @@
     </row>
     <row r="100" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>437</v>
+        <v>122</v>
       </c>
       <c r="B100" s="12" t="s">
         <v>89</v>
@@ -4122,7 +3792,7 @@
     </row>
     <row r="101" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>438</v>
+        <v>122</v>
       </c>
       <c r="B101" s="12" t="s">
         <v>89</v>
@@ -4142,7 +3812,7 @@
     </row>
     <row r="102" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>439</v>
+        <v>122</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>90</v>
@@ -4160,7 +3830,7 @@
     </row>
     <row r="103" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>440</v>
+        <v>122</v>
       </c>
       <c r="B103" s="12" t="s">
         <v>90</v>
@@ -4180,7 +3850,7 @@
     </row>
     <row r="104" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>441</v>
+        <v>122</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>90</v>
@@ -4200,7 +3870,7 @@
     </row>
     <row r="105" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>442</v>
+        <v>122</v>
       </c>
       <c r="B105" s="12" t="s">
         <v>323</v>
@@ -4220,7 +3890,7 @@
     </row>
     <row r="106" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>443</v>
+        <v>122</v>
       </c>
       <c r="B106" s="12" t="s">
         <v>325</v>
@@ -4240,7 +3910,7 @@
     </row>
     <row r="107" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>444</v>
+        <v>122</v>
       </c>
       <c r="B107" s="12" t="s">
         <v>161</v>
@@ -4260,7 +3930,7 @@
     </row>
     <row r="108" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>445</v>
+        <v>122</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>91</v>
@@ -4280,7 +3950,7 @@
     </row>
     <row r="109" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>446</v>
+        <v>122</v>
       </c>
       <c r="B109" s="12" t="s">
         <v>92</v>
@@ -4300,7 +3970,7 @@
     </row>
     <row r="110" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>447</v>
+        <v>122</v>
       </c>
       <c r="B110" s="12" t="s">
         <v>332</v>
@@ -4320,7 +3990,7 @@
     </row>
     <row r="111" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>448</v>
+        <v>122</v>
       </c>
       <c r="B111" s="22" t="s">
         <v>336</v>
@@ -4340,7 +4010,7 @@
     </row>
     <row r="112" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>449</v>
+        <v>122</v>
       </c>
       <c r="B112" s="17" t="s">
         <v>162</v>

--- a/database_manutenzione.xlsx
+++ b/database_manutenzione.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="344">
   <si>
     <t>Scadenza</t>
   </si>
@@ -610,9 +610,6 @@
     <t>Ponte di collegamento, compl. con slitta</t>
   </si>
   <si>
-    <t>Ispezione visiva per rilevamento danneggiamenti, usura dei rivestimenti antiscivolo, etc.</t>
-  </si>
-  <si>
     <t>MR1-08A-TC022</t>
   </si>
   <si>
@@ -1189,6 +1186,12 @@
   </si>
   <si>
     <t>https://app.box.com/s/3fj8wazmw7z9z9neskylu3c9bslfyaxp</t>
+  </si>
+  <si>
+    <t>Ispezione visiva per rilevamento danneggiamenti, usura dei rivestimenti antiscivolo, etc.  1</t>
+  </si>
+  <si>
+    <t>Ispezione visiva per rilevamento danneggiamenti, usura dei rivestimenti antiscivolo, etc.  2</t>
   </si>
 </sst>
 </file>
@@ -1998,7 +2001,7 @@
         <v>187</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>188</v>
+        <v>342</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>185</v>
@@ -2018,7 +2021,7 @@
         <v>128</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>188</v>
+        <v>343</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>185</v>
@@ -2061,13 +2064,13 @@
         <v>62</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E14" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2081,13 +2084,13 @@
         <v>65</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E15" s="14" t="s">
         <v>66</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -2101,13 +2104,13 @@
         <v>131</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E16" s="14" t="s">
         <v>66</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2127,7 +2130,7 @@
         <v>66</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2147,7 +2150,7 @@
         <v>66</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2167,7 +2170,7 @@
         <v>68</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2187,7 +2190,7 @@
         <v>68</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2195,19 +2198,19 @@
         <v>122</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>140</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>141</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2221,13 +2224,13 @@
         <v>143</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>141</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2241,13 +2244,13 @@
         <v>140</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>141</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2255,19 +2258,19 @@
         <v>122</v>
       </c>
       <c r="B24" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="13" t="s">
         <v>204</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>205</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2281,13 +2284,13 @@
         <v>70</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2295,19 +2298,19 @@
         <v>122</v>
       </c>
       <c r="B26" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
         <v>210</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>211</v>
       </c>
       <c r="E26" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2315,19 +2318,19 @@
         <v>122</v>
       </c>
       <c r="B27" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="E27" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2335,19 +2338,19 @@
         <v>122</v>
       </c>
       <c r="B28" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>218</v>
-      </c>
       <c r="D28" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E28" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2355,19 +2358,19 @@
         <v>122</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>71</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2375,19 +2378,19 @@
         <v>122</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>71</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E30" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2395,19 +2398,19 @@
         <v>122</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="D31" s="13" t="s">
         <v>226</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>227</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2415,19 +2418,19 @@
         <v>122</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>230</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2441,13 +2444,13 @@
         <v>72</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2461,13 +2464,13 @@
         <v>73</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>63</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2481,13 +2484,13 @@
         <v>72</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E35" s="24" t="s">
         <v>63</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2507,7 +2510,7 @@
         <v>63</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2527,7 +2530,7 @@
         <v>68</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2535,7 +2538,7 @@
         <v>122</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>146</v>
@@ -2547,7 +2550,7 @@
         <v>68</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2555,19 +2558,19 @@
         <v>122</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2575,7 +2578,7 @@
         <v>122</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C40" s="13" t="s">
         <v>146</v>
@@ -2587,7 +2590,7 @@
         <v>68</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2595,7 +2598,7 @@
         <v>122</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>146</v>
@@ -2607,7 +2610,7 @@
         <v>68</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2615,10 +2618,10 @@
         <v>122</v>
       </c>
       <c r="B42" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>245</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>246</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>47</v>
@@ -2627,7 +2630,7 @@
         <v>68</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2635,19 +2638,19 @@
         <v>122</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>146</v>
       </c>
       <c r="D43" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F43" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2655,7 +2658,7 @@
         <v>122</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>96</v>
@@ -2667,7 +2670,7 @@
         <v>68</v>
       </c>
       <c r="F44" s="21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2675,7 +2678,7 @@
         <v>122</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>146</v>
@@ -2687,7 +2690,7 @@
         <v>68</v>
       </c>
       <c r="F45" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2695,7 +2698,7 @@
         <v>122</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>146</v>
@@ -2707,7 +2710,7 @@
         <v>68</v>
       </c>
       <c r="F46" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2715,10 +2718,10 @@
         <v>122</v>
       </c>
       <c r="B47" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C47" s="13" t="s">
         <v>245</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>246</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>48</v>
@@ -2727,7 +2730,7 @@
         <v>68</v>
       </c>
       <c r="F47" s="21" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2735,7 +2738,7 @@
         <v>122</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>146</v>
@@ -2747,7 +2750,7 @@
         <v>68</v>
       </c>
       <c r="F48" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2755,19 +2758,19 @@
         <v>122</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>97</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2775,19 +2778,19 @@
         <v>122</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>146</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E50" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2795,19 +2798,19 @@
         <v>122</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>146</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2815,19 +2818,19 @@
         <v>122</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E52" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2835,19 +2838,19 @@
         <v>122</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>146</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F53" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2867,7 +2870,7 @@
         <v>68</v>
       </c>
       <c r="F54" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2887,7 +2890,7 @@
         <v>68</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2895,10 +2898,10 @@
         <v>122</v>
       </c>
       <c r="B56" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="C56" s="25" t="s">
         <v>256</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>257</v>
       </c>
       <c r="D56" s="18" t="s">
         <v>50</v>
@@ -2907,7 +2910,7 @@
         <v>68</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2915,19 +2918,19 @@
         <v>122</v>
       </c>
       <c r="B57" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C57" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="D57" s="13" t="s">
         <v>260</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>261</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2935,10 +2938,10 @@
         <v>122</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D58" s="13" t="s">
         <v>50</v>
@@ -2947,7 +2950,7 @@
         <v>68</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2955,10 +2958,10 @@
         <v>122</v>
       </c>
       <c r="B59" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C59" s="13" t="s">
         <v>263</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>264</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>51</v>
@@ -2967,7 +2970,7 @@
         <v>68</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -2975,10 +2978,10 @@
         <v>122</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>51</v>
@@ -2987,7 +2990,7 @@
         <v>68</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="57" x14ac:dyDescent="0.2">
@@ -2998,7 +3001,7 @@
         <v>77</v>
       </c>
       <c r="C61" s="16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D61" s="13" t="s">
         <v>8</v>
@@ -3007,7 +3010,7 @@
         <v>118</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3015,10 +3018,10 @@
         <v>122</v>
       </c>
       <c r="B62" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="C62" s="13" t="s">
         <v>269</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>270</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>52</v>
@@ -3027,7 +3030,7 @@
         <v>118</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3035,10 +3038,10 @@
         <v>122</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>53</v>
@@ -3047,7 +3050,7 @@
         <v>118</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3055,7 +3058,7 @@
         <v>122</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C64" s="13" t="s">
         <v>147</v>
@@ -3067,7 +3070,7 @@
         <v>118</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -3081,13 +3084,13 @@
         <v>114</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>121</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3107,7 +3110,7 @@
         <v>119</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3127,7 +3130,7 @@
         <v>120</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3147,7 +3150,7 @@
         <v>119</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3167,7 +3170,7 @@
         <v>119</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3181,13 +3184,13 @@
         <v>103</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3207,7 +3210,7 @@
         <v>119</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3227,7 +3230,7 @@
         <v>119</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3247,7 +3250,7 @@
         <v>119</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3267,7 +3270,7 @@
         <v>119</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3287,7 +3290,7 @@
         <v>68</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3301,13 +3304,13 @@
         <v>153</v>
       </c>
       <c r="D76" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E76" s="14" t="s">
         <v>119</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -3321,13 +3324,13 @@
         <v>46</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E77" s="14" t="s">
         <v>120</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -3338,7 +3341,7 @@
         <v>82</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D78" s="13" t="s">
         <v>38</v>
@@ -3347,7 +3350,7 @@
         <v>120</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3367,7 +3370,7 @@
         <v>120</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3378,7 +3381,7 @@
         <v>82</v>
       </c>
       <c r="C80" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D80" s="13" t="s">
         <v>55</v>
@@ -3387,7 +3390,7 @@
         <v>120</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="81" spans="1:6" ht="114" x14ac:dyDescent="0.2">
@@ -3398,16 +3401,16 @@
         <v>82</v>
       </c>
       <c r="C81" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>55</v>
       </c>
       <c r="E81" s="27" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="82" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3418,7 +3421,7 @@
         <v>82</v>
       </c>
       <c r="C82" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D82" s="13" t="s">
         <v>55</v>
@@ -3427,7 +3430,7 @@
         <v>120</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3447,7 +3450,7 @@
         <v>119</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3467,7 +3470,7 @@
         <v>119</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3487,7 +3490,7 @@
         <v>119</v>
       </c>
       <c r="F85" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3507,7 +3510,7 @@
         <v>119</v>
       </c>
       <c r="F86" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3527,7 +3530,7 @@
         <v>120</v>
       </c>
       <c r="F87" s="21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3547,7 +3550,7 @@
         <v>119</v>
       </c>
       <c r="F88" s="21" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3567,7 +3570,7 @@
         <v>119</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3587,7 +3590,7 @@
         <v>119</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="91" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3607,7 +3610,7 @@
         <v>119</v>
       </c>
       <c r="F91" s="21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3627,7 +3630,7 @@
         <v>68</v>
       </c>
       <c r="F92" s="21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3638,7 +3641,7 @@
         <v>87</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D93" s="13" t="s">
         <v>15</v>
@@ -3647,7 +3650,7 @@
         <v>68</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3661,13 +3664,13 @@
         <v>108</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E94" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F94" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3687,7 +3690,7 @@
         <v>120</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3707,7 +3710,7 @@
         <v>120</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3715,7 +3718,7 @@
         <v>122</v>
       </c>
       <c r="B97" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C97" s="13" t="s">
         <v>111</v>
@@ -3727,7 +3730,7 @@
         <v>118</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -3735,7 +3738,7 @@
         <v>122</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C98" s="13" t="s">
         <v>112</v>
@@ -3747,7 +3750,7 @@
         <v>118</v>
       </c>
       <c r="F98" s="21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3767,7 +3770,7 @@
         <v>120</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -3778,16 +3781,16 @@
         <v>89</v>
       </c>
       <c r="C100" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="D100" s="13" t="s">
         <v>316</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>317</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>120</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3807,7 +3810,7 @@
         <v>120</v>
       </c>
       <c r="F101" s="21" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3821,7 +3824,7 @@
         <v>113</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E102" s="14" t="s">
         <v>120</v>
@@ -3836,7 +3839,7 @@
         <v>90</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D103" s="13" t="s">
         <v>21</v>
@@ -3845,7 +3848,7 @@
         <v>120</v>
       </c>
       <c r="F103" s="21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3865,7 +3868,7 @@
         <v>120</v>
       </c>
       <c r="F104" s="21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3873,7 +3876,7 @@
         <v>122</v>
       </c>
       <c r="B105" s="12" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C105" s="13" t="s">
         <v>46</v>
@@ -3885,7 +3888,7 @@
         <v>63</v>
       </c>
       <c r="F105" s="21" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3893,10 +3896,10 @@
         <v>122</v>
       </c>
       <c r="B106" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C106" s="16" t="s">
         <v>325</v>
-      </c>
-      <c r="C106" s="16" t="s">
-        <v>326</v>
       </c>
       <c r="D106" s="13" t="s">
         <v>58</v>
@@ -3905,7 +3908,7 @@
         <v>63</v>
       </c>
       <c r="F106" s="21" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3916,7 +3919,7 @@
         <v>161</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D107" s="13" t="s">
         <v>44</v>
@@ -3925,7 +3928,7 @@
         <v>63</v>
       </c>
       <c r="F107" s="21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -3936,7 +3939,7 @@
         <v>91</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D108" s="13" t="s">
         <v>22</v>
@@ -3945,7 +3948,7 @@
         <v>63</v>
       </c>
       <c r="F108" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3965,7 +3968,7 @@
         <v>68</v>
       </c>
       <c r="F109" s="21" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3973,19 +3976,19 @@
         <v>122</v>
       </c>
       <c r="B110" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="C110" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="D110" s="13" t="s">
         <v>333</v>
-      </c>
-      <c r="D110" s="13" t="s">
-        <v>334</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>68</v>
       </c>
       <c r="F110" s="21" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -3993,10 +3996,10 @@
         <v>122</v>
       </c>
       <c r="B111" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="C111" s="23" t="s">
         <v>336</v>
-      </c>
-      <c r="C111" s="23" t="s">
-        <v>337</v>
       </c>
       <c r="D111" s="23" t="s">
         <v>59</v>
@@ -4005,7 +4008,7 @@
         <v>68</v>
       </c>
       <c r="F111" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="112" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
@@ -4025,7 +4028,7 @@
         <v>68</v>
       </c>
       <c r="F112" s="21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.2">

--- a/database_manutenzione.xlsx
+++ b/database_manutenzione.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="345">
   <si>
     <t>Scadenza</t>
   </si>
@@ -1192,6 +1192,9 @@
   </si>
   <si>
     <t>Ispezione visiva per rilevamento danneggiamenti, usura dei rivestimenti antiscivolo, etc.  2</t>
+  </si>
+  <si>
+    <t>https://app.box.com/s/x9mqn6k01o1vr7mqrdwrvo872hd8f474</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1400,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1417,12 +1420,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1470,9 +1467,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1787,8 +1781,8 @@
     <col min="1" max="1" width="9.42578125" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="88.28515625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="110" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="4"/>
   </cols>
@@ -1817,19 +1811,19 @@
       <c r="A2" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="13" t="s">
         <v>167</v>
       </c>
     </row>
@@ -1837,19 +1831,19 @@
       <c r="A3" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="13" t="s">
         <v>170</v>
       </c>
     </row>
@@ -1857,19 +1851,19 @@
       <c r="A4" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="15" t="s">
+      <c r="E4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>172</v>
       </c>
     </row>
@@ -1877,19 +1871,19 @@
       <c r="A5" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="13" t="s">
         <v>174</v>
       </c>
     </row>
@@ -1897,19 +1891,19 @@
       <c r="A6" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="13" t="s">
         <v>176</v>
       </c>
     </row>
@@ -1917,19 +1911,19 @@
       <c r="A7" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="13" t="s">
         <v>180</v>
       </c>
     </row>
@@ -1937,19 +1931,19 @@
       <c r="A8" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="13" t="s">
         <v>184</v>
       </c>
     </row>
@@ -1957,19 +1951,19 @@
       <c r="A9" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E9" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="15" t="s">
+      <c r="E9" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="13" t="s">
         <v>186</v>
       </c>
     </row>
@@ -1977,19 +1971,19 @@
       <c r="A10" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E10" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="15" t="s">
+      <c r="E10" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>186</v>
       </c>
     </row>
@@ -1997,19 +1991,19 @@
       <c r="A11" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E11" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="15" t="s">
+      <c r="E11" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="13" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2017,19 +2011,19 @@
       <c r="A12" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E12" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F12" s="15" t="s">
+      <c r="E12" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2037,19 +2031,19 @@
       <c r="A13" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F13" s="15" t="s">
+      <c r="E13" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="13" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2057,19 +2051,19 @@
       <c r="A14" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="13" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2077,19 +2071,19 @@
       <c r="A15" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="E15" s="14" t="s">
+      <c r="E15" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="13" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2097,19 +2091,19 @@
       <c r="A16" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="13" t="s">
         <v>193</v>
       </c>
     </row>
@@ -2117,19 +2111,19 @@
       <c r="A17" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>194</v>
       </c>
     </row>
@@ -2137,19 +2131,19 @@
       <c r="A18" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="13" t="s">
         <v>195</v>
       </c>
     </row>
@@ -2157,19 +2151,19 @@
       <c r="A19" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="15" t="s">
+      <c r="E19" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="13" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2177,19 +2171,19 @@
       <c r="A20" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="15" t="s">
+      <c r="E20" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>196</v>
       </c>
     </row>
@@ -2197,19 +2191,19 @@
       <c r="A21" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="13" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2217,19 +2211,19 @@
       <c r="A22" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="13" t="s">
         <v>199</v>
       </c>
     </row>
@@ -2237,19 +2231,19 @@
       <c r="A23" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="13" t="s">
         <v>201</v>
       </c>
     </row>
@@ -2257,19 +2251,19 @@
       <c r="A24" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="21" t="s">
+      <c r="E24" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="19" t="s">
         <v>205</v>
       </c>
     </row>
@@ -2277,19 +2271,19 @@
       <c r="A25" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="21" t="s">
+      <c r="E25" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="19" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2297,19 +2291,19 @@
       <c r="A26" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F26" s="21" t="s">
+      <c r="E26" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="19" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2317,19 +2311,19 @@
       <c r="A27" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F27" s="21" t="s">
+      <c r="E27" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" s="19" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2337,19 +2331,19 @@
       <c r="A28" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="19" t="s">
         <v>215</v>
       </c>
     </row>
@@ -2357,19 +2351,19 @@
       <c r="A29" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E29" s="14" t="s">
+      <c r="E29" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="19" t="s">
         <v>220</v>
       </c>
     </row>
@@ -2377,19 +2371,19 @@
       <c r="A30" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="E30" s="14" t="s">
+      <c r="E30" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="19" t="s">
         <v>223</v>
       </c>
     </row>
@@ -2397,19 +2391,19 @@
       <c r="A31" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="E31" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="19" t="s">
         <v>227</v>
       </c>
     </row>
@@ -2417,19 +2411,19 @@
       <c r="A32" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="19" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2437,19 +2431,19 @@
       <c r="A33" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="19" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2457,19 +2451,19 @@
       <c r="A34" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="E34" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="19" t="s">
         <v>232</v>
       </c>
     </row>
@@ -2477,19 +2471,19 @@
       <c r="A35" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="C35" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="D35" s="23" t="s">
+      <c r="D35" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="19" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2497,19 +2491,19 @@
       <c r="A36" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="E36" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="19" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2517,19 +2511,19 @@
       <c r="A37" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37" s="21" t="s">
+      <c r="E37" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F37" s="19" t="s">
         <v>235</v>
       </c>
     </row>
@@ -2537,19 +2531,19 @@
       <c r="A38" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F38" s="21" t="s">
+      <c r="E38" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F38" s="19" t="s">
         <v>237</v>
       </c>
     </row>
@@ -2557,19 +2551,19 @@
       <c r="A39" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F39" s="21" t="s">
+      <c r="E39" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2577,19 +2571,19 @@
       <c r="A40" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D40" s="13" t="s">
+      <c r="D40" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F40" s="21" t="s">
+      <c r="E40" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F40" s="19" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2597,19 +2591,19 @@
       <c r="A41" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E41" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F41" s="21" t="s">
+      <c r="E41" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F41" s="19" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2617,19 +2611,19 @@
       <c r="A42" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E42" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F42" s="21" t="s">
+      <c r="E42" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2637,19 +2631,19 @@
       <c r="A43" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="E43" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F43" s="21" t="s">
+      <c r="E43" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F43" s="19" t="s">
         <v>248</v>
       </c>
     </row>
@@ -2657,19 +2651,19 @@
       <c r="A44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E44" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F44" s="21" t="s">
+      <c r="E44" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="19" t="s">
         <v>249</v>
       </c>
     </row>
@@ -2677,19 +2671,19 @@
       <c r="A45" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F45" s="21" t="s">
+      <c r="E45" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="19" t="s">
         <v>250</v>
       </c>
     </row>
@@ -2697,19 +2691,19 @@
       <c r="A46" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F46" s="21" t="s">
+      <c r="E46" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F46" s="19" t="s">
         <v>250</v>
       </c>
     </row>
@@ -2717,19 +2711,19 @@
       <c r="A47" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E47" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F47" s="21" t="s">
+      <c r="E47" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F47" s="19" t="s">
         <v>250</v>
       </c>
     </row>
@@ -2737,19 +2731,19 @@
       <c r="A48" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E48" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F48" s="21" t="s">
+      <c r="E48" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F48" s="19" t="s">
         <v>251</v>
       </c>
     </row>
@@ -2757,19 +2751,19 @@
       <c r="A49" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="18" t="s">
         <v>238</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F49" s="21" t="s">
+      <c r="E49" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F49" s="19" t="s">
         <v>240</v>
       </c>
     </row>
@@ -2777,19 +2771,19 @@
       <c r="A50" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="13" t="s">
+      <c r="C50" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D50" s="13" t="s">
+      <c r="D50" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E50" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F50" s="21" t="s">
+      <c r="E50" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F50" s="19" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2797,19 +2791,19 @@
       <c r="A51" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F51" s="21" t="s">
+      <c r="E51" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F51" s="19" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2817,19 +2811,19 @@
       <c r="A52" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F52" s="21" t="s">
+      <c r="E52" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F52" s="19" t="s">
         <v>242</v>
       </c>
     </row>
@@ -2837,19 +2831,19 @@
       <c r="A53" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="E53" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" s="21" t="s">
+      <c r="E53" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F53" s="19" t="s">
         <v>248</v>
       </c>
     </row>
@@ -2857,19 +2851,19 @@
       <c r="A54" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="D54" s="13" t="s">
+      <c r="D54" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F54" s="21" t="s">
+      <c r="E54" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F54" s="19" t="s">
         <v>254</v>
       </c>
     </row>
@@ -2877,19 +2871,19 @@
       <c r="A55" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="22" t="s">
+      <c r="B55" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="D55" s="23" t="s">
+      <c r="D55" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="F55" s="21" t="s">
+      <c r="E55" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F55" s="19" t="s">
         <v>254</v>
       </c>
     </row>
@@ -2897,19 +2891,19 @@
       <c r="A56" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C56" s="25" t="s">
+      <c r="C56" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E56" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F56" s="21" t="s">
+      <c r="E56" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F56" s="19" t="s">
         <v>257</v>
       </c>
     </row>
@@ -2917,19 +2911,19 @@
       <c r="A57" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="C57" s="13" t="s">
+      <c r="C57" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="D57" s="13" t="s">
+      <c r="D57" s="11" t="s">
         <v>260</v>
       </c>
-      <c r="E57" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F57" s="21" t="s">
+      <c r="E57" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F57" s="19" t="s">
         <v>257</v>
       </c>
     </row>
@@ -2937,19 +2931,19 @@
       <c r="A58" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="D58" s="13" t="s">
+      <c r="D58" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E58" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F58" s="21" t="s">
+      <c r="E58" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" s="19" t="s">
         <v>257</v>
       </c>
     </row>
@@ -2957,19 +2951,19 @@
       <c r="A59" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C59" s="13" t="s">
+      <c r="C59" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D59" s="13" t="s">
+      <c r="D59" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E59" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F59" s="21" t="s">
+      <c r="E59" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="19" t="s">
         <v>264</v>
       </c>
     </row>
@@ -2977,19 +2971,19 @@
       <c r="A60" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C60" s="13" t="s">
+      <c r="C60" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="D60" s="13" t="s">
+      <c r="D60" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E60" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F60" s="21" t="s">
+      <c r="E60" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" s="19" t="s">
         <v>264</v>
       </c>
     </row>
@@ -2997,19 +2991,19 @@
       <c r="A61" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="D61" s="13" t="s">
+      <c r="D61" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E61" s="14" t="s">
+      <c r="E61" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F61" s="21" t="s">
+      <c r="F61" s="19" t="s">
         <v>267</v>
       </c>
     </row>
@@ -3017,19 +3011,19 @@
       <c r="A62" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="20" t="s">
+      <c r="B62" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="C62" s="13" t="s">
+      <c r="C62" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D62" s="13" t="s">
+      <c r="D62" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F62" s="21" t="s">
+      <c r="F62" s="19" t="s">
         <v>270</v>
       </c>
     </row>
@@ -3037,19 +3031,19 @@
       <c r="A63" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="C63" s="13" t="s">
+      <c r="C63" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D63" s="13" t="s">
+      <c r="D63" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F63" s="21" t="s">
+      <c r="F63" s="19" t="s">
         <v>272</v>
       </c>
     </row>
@@ -3057,19 +3051,19 @@
       <c r="A64" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D64" s="13" t="s">
+      <c r="D64" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E64" s="14" t="s">
+      <c r="E64" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F64" s="21" t="s">
+      <c r="F64" s="19" t="s">
         <v>274</v>
       </c>
     </row>
@@ -3077,19 +3071,19 @@
       <c r="A65" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="F65" s="15" t="s">
+      <c r="F65" s="13" t="s">
         <v>340</v>
       </c>
     </row>
@@ -3097,19 +3091,19 @@
       <c r="A66" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C66" s="13" t="s">
+      <c r="C66" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="D66" s="13" t="s">
+      <c r="D66" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F66" s="21" t="s">
+      <c r="F66" s="19" t="s">
         <v>276</v>
       </c>
     </row>
@@ -3117,19 +3111,19 @@
       <c r="A67" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F67" s="21" t="s">
+      <c r="F67" s="19" t="s">
         <v>276</v>
       </c>
     </row>
@@ -3137,19 +3131,19 @@
       <c r="A68" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C68" s="13" t="s">
+      <c r="C68" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="D68" s="13" t="s">
+      <c r="D68" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E68" s="14" t="s">
+      <c r="E68" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F68" s="21" t="s">
+      <c r="F68" s="19" t="s">
         <v>277</v>
       </c>
     </row>
@@ -3157,19 +3151,19 @@
       <c r="A69" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C69" s="13" t="s">
+      <c r="C69" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D69" s="13" t="s">
+      <c r="D69" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E69" s="14" t="s">
+      <c r="E69" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F69" s="21" t="s">
+      <c r="F69" s="19" t="s">
         <v>278</v>
       </c>
     </row>
@@ -3177,19 +3171,19 @@
       <c r="A70" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C70" s="13" t="s">
+      <c r="C70" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D70" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="E70" s="14" t="s">
+      <c r="E70" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F70" s="21" t="s">
+      <c r="F70" s="19" t="s">
         <v>280</v>
       </c>
     </row>
@@ -3197,19 +3191,19 @@
       <c r="A71" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="D71" s="13" t="s">
+      <c r="D71" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E71" s="14" t="s">
+      <c r="E71" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F71" s="21" t="s">
+      <c r="F71" s="19" t="s">
         <v>281</v>
       </c>
     </row>
@@ -3217,19 +3211,19 @@
       <c r="A72" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="13" t="s">
+      <c r="C72" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="D72" s="13" t="s">
+      <c r="D72" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E72" s="14" t="s">
+      <c r="E72" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="F72" s="19" t="s">
         <v>282</v>
       </c>
     </row>
@@ -3237,19 +3231,19 @@
       <c r="A73" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B73" s="22" t="s">
+      <c r="B73" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="D73" s="23" t="s">
+      <c r="D73" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="22" t="s">
         <v>119</v>
       </c>
-      <c r="F73" s="21" t="s">
+      <c r="F73" s="19" t="s">
         <v>283</v>
       </c>
     </row>
@@ -3257,19 +3251,19 @@
       <c r="A74" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="D74" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F74" s="21" t="s">
+      <c r="F74" s="19" t="s">
         <v>284</v>
       </c>
     </row>
@@ -3277,19 +3271,19 @@
       <c r="A75" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C75" s="13" t="s">
+      <c r="C75" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D75" s="13" t="s">
+      <c r="D75" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E75" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F75" s="21" t="s">
+      <c r="E75" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F75" s="19" t="s">
         <v>285</v>
       </c>
     </row>
@@ -3297,19 +3291,19 @@
       <c r="A76" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="D76" s="13" t="s">
+      <c r="D76" s="11" t="s">
         <v>286</v>
       </c>
-      <c r="E76" s="14" t="s">
+      <c r="E76" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F76" s="15" t="s">
+      <c r="F76" s="13" t="s">
         <v>341</v>
       </c>
     </row>
@@ -3317,19 +3311,19 @@
       <c r="A77" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D77" s="13" t="s">
+      <c r="D77" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F77" s="15" t="s">
+      <c r="F77" s="13" t="s">
         <v>339</v>
       </c>
     </row>
@@ -3337,19 +3331,19 @@
       <c r="A78" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="D78" s="13" t="s">
+      <c r="D78" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F78" s="21" t="s">
+      <c r="F78" s="19" t="s">
         <v>289</v>
       </c>
     </row>
@@ -3357,19 +3351,19 @@
       <c r="A79" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D79" s="13" t="s">
+      <c r="D79" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E79" s="14" t="s">
+      <c r="E79" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F79" s="21" t="s">
+      <c r="F79" s="19" t="s">
         <v>290</v>
       </c>
     </row>
@@ -3377,19 +3371,19 @@
       <c r="A80" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="D80" s="13" t="s">
+      <c r="D80" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F80" s="21" t="s">
+      <c r="F80" s="19" t="s">
         <v>292</v>
       </c>
     </row>
@@ -3397,19 +3391,19 @@
       <c r="A81" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="D81" s="13" t="s">
+      <c r="D81" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E81" s="27" t="s">
+      <c r="E81" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="F81" s="21" t="s">
+      <c r="F81" s="19" t="s">
         <v>292</v>
       </c>
     </row>
@@ -3417,19 +3411,19 @@
       <c r="A82" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="D82" s="13" t="s">
+      <c r="D82" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E82" s="14" t="s">
+      <c r="E82" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F82" s="21" t="s">
+      <c r="F82" s="19" t="s">
         <v>292</v>
       </c>
     </row>
@@ -3437,19 +3431,19 @@
       <c r="A83" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="D83" s="13" t="s">
+      <c r="D83" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E83" s="14" t="s">
+      <c r="E83" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F83" s="21" t="s">
+      <c r="F83" s="19" t="s">
         <v>296</v>
       </c>
     </row>
@@ -3457,19 +3451,19 @@
       <c r="A84" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D84" s="13" t="s">
+      <c r="D84" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E84" s="14" t="s">
+      <c r="E84" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F84" s="21" t="s">
+      <c r="F84" s="19" t="s">
         <v>297</v>
       </c>
     </row>
@@ -3477,19 +3471,19 @@
       <c r="A85" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="13" t="s">
+      <c r="C85" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D85" s="13" t="s">
+      <c r="D85" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="14" t="s">
+      <c r="E85" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F85" s="21" t="s">
+      <c r="F85" s="19" t="s">
         <v>298</v>
       </c>
     </row>
@@ -3497,19 +3491,19 @@
       <c r="A86" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C86" s="13" t="s">
+      <c r="C86" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D86" s="13" t="s">
+      <c r="D86" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="E86" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F86" s="21" t="s">
+      <c r="F86" s="19" t="s">
         <v>299</v>
       </c>
     </row>
@@ -3517,19 +3511,19 @@
       <c r="A87" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C87" s="13" t="s">
+      <c r="C87" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D87" s="13" t="s">
+      <c r="D87" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E87" s="14" t="s">
+      <c r="E87" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F87" s="21" t="s">
+      <c r="F87" s="19" t="s">
         <v>299</v>
       </c>
     </row>
@@ -3537,19 +3531,19 @@
       <c r="A88" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D88" s="13" t="s">
+      <c r="D88" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="E88" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F88" s="21" t="s">
+      <c r="F88" s="19" t="s">
         <v>300</v>
       </c>
     </row>
@@ -3557,19 +3551,19 @@
       <c r="A89" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E89" s="14" t="s">
+      <c r="E89" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F89" s="21" t="s">
+      <c r="F89" s="19" t="s">
         <v>301</v>
       </c>
     </row>
@@ -3577,19 +3571,19 @@
       <c r="A90" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D90" s="13" t="s">
+      <c r="D90" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E90" s="14" t="s">
+      <c r="E90" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F90" s="21" t="s">
+      <c r="F90" s="19" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3597,19 +3591,19 @@
       <c r="A91" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C91" s="13" t="s">
+      <c r="C91" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D91" s="13" t="s">
+      <c r="D91" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E91" s="14" t="s">
+      <c r="E91" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="F91" s="21" t="s">
+      <c r="F91" s="19" t="s">
         <v>303</v>
       </c>
     </row>
@@ -3617,19 +3611,19 @@
       <c r="A92" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D92" s="13" t="s">
+      <c r="D92" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E92" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F92" s="21" t="s">
+      <c r="E92" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F92" s="19" t="s">
         <v>304</v>
       </c>
     </row>
@@ -3637,19 +3631,19 @@
       <c r="A93" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C93" s="16" t="s">
+      <c r="C93" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D93" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E93" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F93" s="21" t="s">
+      <c r="E93" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F93" s="19" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3657,19 +3651,19 @@
       <c r="A94" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D94" s="13" t="s">
+      <c r="D94" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="E94" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F94" s="21" t="s">
+      <c r="E94" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F94" s="19" t="s">
         <v>308</v>
       </c>
     </row>
@@ -3677,19 +3671,19 @@
       <c r="A95" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B95" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C95" s="18" t="s">
+      <c r="C95" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D95" s="18" t="s">
+      <c r="D95" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="E95" s="19" t="s">
+      <c r="E95" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="F95" s="21" t="s">
+      <c r="F95" s="19" t="s">
         <v>309</v>
       </c>
     </row>
@@ -3697,19 +3691,19 @@
       <c r="A96" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="13" t="s">
+      <c r="D96" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E96" s="14" t="s">
+      <c r="E96" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F96" s="21" t="s">
+      <c r="F96" s="19" t="s">
         <v>310</v>
       </c>
     </row>
@@ -3717,19 +3711,19 @@
       <c r="A97" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="C97" s="13" t="s">
+      <c r="C97" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="D97" s="13" t="s">
+      <c r="D97" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E97" s="14" t="s">
+      <c r="E97" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F97" s="21" t="s">
+      <c r="F97" s="19" t="s">
         <v>310</v>
       </c>
     </row>
@@ -3737,19 +3731,19 @@
       <c r="A98" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B98" s="20" t="s">
+      <c r="B98" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C98" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D98" s="13" t="s">
+      <c r="D98" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E98" s="14" t="s">
+      <c r="E98" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="F98" s="21" t="s">
+      <c r="F98" s="19" t="s">
         <v>313</v>
       </c>
     </row>
@@ -3757,19 +3751,19 @@
       <c r="A99" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C99" s="13" t="s">
+      <c r="C99" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D99" s="13" t="s">
+      <c r="D99" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E99" s="14" t="s">
+      <c r="E99" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F99" s="21" t="s">
+      <c r="F99" s="19" t="s">
         <v>314</v>
       </c>
     </row>
@@ -3777,19 +3771,19 @@
       <c r="A100" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C100" s="16" t="s">
+      <c r="C100" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="D100" s="13" t="s">
+      <c r="D100" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="E100" s="14" t="s">
+      <c r="E100" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F100" s="21" t="s">
+      <c r="F100" s="19" t="s">
         <v>317</v>
       </c>
     </row>
@@ -3797,57 +3791,59 @@
       <c r="A101" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="C101" s="13" t="s">
+      <c r="C101" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D101" s="13" t="s">
+      <c r="D101" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E101" s="14" t="s">
+      <c r="E101" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F101" s="21" t="s">
+      <c r="F101" s="19" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="102" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="D102" s="13" t="s">
+      <c r="D102" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="E102" s="14" t="s">
+      <c r="E102" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F102" s="26"/>
+      <c r="F102" s="13" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="103" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C103" s="16" t="s">
+      <c r="C103" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="D103" s="13" t="s">
+      <c r="D103" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E103" s="14" t="s">
+      <c r="E103" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F103" s="21" t="s">
+      <c r="F103" s="19" t="s">
         <v>320</v>
       </c>
     </row>
@@ -3855,19 +3851,19 @@
       <c r="A104" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C104" s="13" t="s">
+      <c r="C104" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D104" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E104" s="14" t="s">
+      <c r="E104" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="F104" s="21" t="s">
+      <c r="F104" s="19" t="s">
         <v>321</v>
       </c>
     </row>
@@ -3875,19 +3871,19 @@
       <c r="A105" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C105" s="13" t="s">
+      <c r="C105" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D105" s="13" t="s">
+      <c r="D105" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E105" s="14" t="s">
+      <c r="E105" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F105" s="21" t="s">
+      <c r="F105" s="19" t="s">
         <v>323</v>
       </c>
     </row>
@@ -3895,19 +3891,19 @@
       <c r="A106" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="C106" s="16" t="s">
+      <c r="C106" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="D106" s="13" t="s">
+      <c r="D106" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E106" s="14" t="s">
+      <c r="E106" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F106" s="21" t="s">
+      <c r="F106" s="19" t="s">
         <v>326</v>
       </c>
     </row>
@@ -3915,19 +3911,19 @@
       <c r="A107" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C107" s="16" t="s">
+      <c r="C107" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="D107" s="13" t="s">
+      <c r="D107" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E107" s="14" t="s">
+      <c r="E107" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F107" s="21" t="s">
+      <c r="F107" s="19" t="s">
         <v>327</v>
       </c>
     </row>
@@ -3935,19 +3931,19 @@
       <c r="A108" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="C108" s="16" t="s">
+      <c r="C108" s="14" t="s">
         <v>328</v>
       </c>
-      <c r="D108" s="13" t="s">
+      <c r="D108" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E108" s="14" t="s">
+      <c r="E108" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F108" s="21" t="s">
+      <c r="F108" s="19" t="s">
         <v>329</v>
       </c>
     </row>
@@ -3955,19 +3951,19 @@
       <c r="A109" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="D109" s="13" t="s">
+      <c r="D109" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E109" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F109" s="21" t="s">
+      <c r="E109" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F109" s="19" t="s">
         <v>330</v>
       </c>
     </row>
@@ -3975,19 +3971,19 @@
       <c r="A110" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="C110" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="D110" s="13" t="s">
+      <c r="D110" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="E110" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F110" s="21" t="s">
+      <c r="E110" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F110" s="19" t="s">
         <v>334</v>
       </c>
     </row>
@@ -3995,19 +3991,19 @@
       <c r="A111" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B111" s="22" t="s">
+      <c r="B111" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="C111" s="23" t="s">
+      <c r="C111" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="D111" s="23" t="s">
+      <c r="D111" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E111" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="F111" s="21" t="s">
+      <c r="E111" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F111" s="19" t="s">
         <v>337</v>
       </c>
     </row>
@@ -4015,175 +4011,21 @@
       <c r="A112" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B112" s="17" t="s">
+      <c r="B112" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C112" s="18" t="s">
+      <c r="C112" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="D112" s="18" t="s">
+      <c r="D112" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="E112" s="19" t="s">
-        <v>68</v>
-      </c>
-      <c r="F112" s="21" t="s">
+      <c r="E112" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F112" s="19" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B113" s="7"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="2"/>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B114" s="7"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="2"/>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B115" s="8"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="2"/>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B116" s="8"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="2"/>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B117" s="7"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="2"/>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B118" s="7"/>
-      <c r="C118" s="9"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="2"/>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B119" s="7"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="2"/>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B120" s="7"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="2"/>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B121" s="7"/>
-      <c r="C121" s="9"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="2"/>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B122" s="7"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="2"/>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B123" s="7"/>
-      <c r="C123" s="9"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="2"/>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B124" s="7"/>
-      <c r="C124" s="9"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="2"/>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B125" s="7"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="2"/>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B126" s="7"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="2"/>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B127" s="7"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="7"/>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B128" s="7"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="7"/>
-    </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B129" s="7"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="7"/>
-    </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B130" s="7"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="7"/>
-    </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B131" s="7"/>
-      <c r="C131" s="9"/>
-      <c r="D131" s="7"/>
-    </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B132" s="7"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="7"/>
-    </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B133" s="7"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="7"/>
-    </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B134" s="7"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="7"/>
-    </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B135" s="7"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="7"/>
-    </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B136" s="7"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="7"/>
-    </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B137" s="7"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="7"/>
-    </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B138" s="7"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="7"/>
-    </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B139" s="7"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="7"/>
-    </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B140" s="7"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="7"/>
     </row>
     <row r="244" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B244" s="2"/>
@@ -4198,13 +4040,13 @@
       <c r="E245" s="3"/>
     </row>
     <row r="246" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B246" s="10"/>
+      <c r="B246" s="8"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="7"/>
     </row>
     <row r="247" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B247" s="10"/>
+      <c r="B247" s="8"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="7"/>
@@ -4235,7 +4077,7 @@
     </row>
     <row r="252" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B252" s="2"/>
-      <c r="C252" s="10"/>
+      <c r="C252" s="8"/>
       <c r="D252" s="2"/>
       <c r="E252" s="7"/>
     </row>
@@ -4270,7 +4112,7 @@
       <c r="E257" s="3"/>
     </row>
     <row r="258" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D258" s="11"/>
+      <c r="D258" s="9"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4382,8 +4224,9 @@
     <hyperlink ref="F77" r:id="rId106"/>
     <hyperlink ref="F65" r:id="rId107"/>
     <hyperlink ref="F76" r:id="rId108"/>
+    <hyperlink ref="F102" r:id="rId109"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId109"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId110"/>
 </worksheet>
 </file>